--- a/data/berita_2026-08-12.xlsx
+++ b/data/berita_2026-08-12.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -997,8 +997,384 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubes Witjaksono tegaskan tekad ASEAN perkuat kemitraan dengan Kenya</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 01:27:25 +0700</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Duta Besar RI untuk Kenya TBH Witjaksono Adji menegaskan komitmen ASEAN untuk terus memperluas kemitraan di luar ...</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690117/dubes-witjaksono-tegaskan-tekad-asean-perkuat-kemitraan-dengan-kenya</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/WhatsApp-Image-2026-08-11-at-19.08.43.jpeg</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Menhub pastikan seluruh rekomendasi BPK ditindaklanjuti</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 01:17:22 +0700</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Menteri Perhubungan (Menhub) Dudy Purwagandhi memastikan seluruh rekomendasi Badan Pemeriksa Keuangan (BPK) ...</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690113/menhub-pastikan-seluruh-rekomendasi-bpk-ditindaklanjuti</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/9A3CF4B6-CCC1-4215-AD4D-0C7AA714D87F.jpeg</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kemensetneg gelar rapat pleno, matangkan rangkaian peringatan HUT RI</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 01:12:53 +0700</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Kementerian Sekretariat Negara menggelar rapat pleno persiapan rangkaian Bulan Kemerdekaan menjelang peringatan HUT ...</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690111/kemensetneg-gelar-rapat-pleno-matangkan-rangkaian-peringatan-hut-ri</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/1000404279.jpg</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>7 Kantor Pemkab Puncak Papua Tengah Dibakar Massa: Gedung Bupati-DPRD</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 01:24:48 +0700</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Paulus Pulo</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Massa membakar tujuh kantor pemerintah di Puncak, Papua Tengah, termasuk Kantor Bupati dan DPRD, akibat ketidakpuasan pembagian dana desa.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614538/7-kantor-pemkab-puncak-papua-tengah-dibakar-massa-gedung-bupati-dprd</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/gedung-pemerintahan-di-puncak-papua-tengah-dibakar-massa-1786452308073_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kemenhut Ungkap Jual-Beli Lahan Hutan Lindung di Sulsel, 3 Orang Ditangkap</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 01:01:12 +0700</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Kemenhut ungkap modus jual-beli lahan hutan lindung di Sulsel. Tiga pelaku ditangkap saat menggarap lahan ilegal.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614536/kemenhut-ungkap-jual-beli-lahan-hutan-lindung-di-sulsel-3-orang-ditangkap</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/12/kemenhut-ungkap-modus-jual-beli-lahan-hutan-lindung-di-sulsel-dok-antara-1786469730093_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Peringatan ke Pegawai, Gus Ipul: Jangan Kebiasaan Habiskan Uang dan Belanja Sembarangan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 01:47:38 +0700</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Mensos Saifullah Yusuf atau Gus Ipul memperingatkan pegawainya agar meninggalkan kebiasaan menghabiskan uang dan belanja anggaran secara sembarangan.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/11/23324151/peringatan-ke-pegawai-gus-ipul-jangan-kebiasaan-habiskan-uang-dan-belanja</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/pKspNR1Miw68Cgbca6xdXgMI_PM=/425x148:3753x2367/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a73165e5e027.jpeg</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Perang AS Temui Menhan Sjafrie, Bahas soal Kelanjutan Kerja Sama Pertahanan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 01:47:38 +0700</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Perang Amerika Serikat (AS) bidang Kebijakan Elbridge A. Colby mengunjungi Menteri Pertahanan RI Sjafrie Sjamsoeddin di Kemenhan RI.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/11/22202711/wakil-menteri-perang-as-temui-menhan-sjafrie-bahas-soal-kelanjutan-kerja</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/d6iy2gqD10-O_Sn9zLIxhlhGQOI=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/11/6a7b340b0529f.jpg</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Rinaldi Umar Batal Dilantik Jadi Dirdik Jampidsus, Ini Alasan Kejagung</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 01:47:38 +0700</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Alasan Rinaldi Umar batal dilantik sebagai Direktur Penyidikan (Dirdik) pada Jaksa Agung Muda Tindak Pidana Khusus karena alasan pengalaman.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/11/21262681/rinaldi-umar-batal-dilantik-jadi-dirdik-jampidsus-ini-alasan-kejagung</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/RkjlvY0ly1nBMPQx3Rv8uJ7Vyts=/265x66:1297x754/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/03/6a70a42491bfb.jpg</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I12"/>
+  <autoFilter ref="A1:I20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-12.xlsx
+++ b/data/berita_2026-08-12.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1373,8 +1373,337 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Mengunjungi Museum Linggam Cahaya, mengulik sejarah mata uang SKR</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 01:54:39 +0700</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ANTARA - Di sebuah pulau di Kabupaten Lingga, Kepulauan Riau, berdiri sebuah Museum Linggam Cahaya Pulau Daik ...</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5690120/mengunjungi-museum-linggam-cahaya-mengulik-sejarah-mata-uang-skr</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/MENGUNJUNGI-MUSEUM-LINGGAM-CAHAYA-MENGULIK-SEJARAH-MATA-UANG-SKR.jpg</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Polisi Kumpulkan Barang Bukti Terkait Kasus Hafalan Qur'an demi Miras</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 02:34:34 +0700</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Polisi selidiki dugaan penistaan agama terkait challenge hafalan Al-Qur'an demi miras di festival musik Ancol. Barang bukti sedang dikumpulkan.</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614542/polisi-kumpulkan-barang-bukti-terkait-kasus-hafalan-quran-demi-miras</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/04/09/waduh-di-china-ada-tren-baru-mukbang-minum-miras-yang-berbahaya-3_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kemlu: 3 ABK WNI Diserang Rudal Houthi di Selat Bab Al-Mandeb</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 02:02:55 +0700</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Kemlu RI mengonfirmasi serangan Houthi di Selat Al-Mandeb yang melibatkan tiga ABK WNI. Dua dilaporkan terluka dan satu dilaporkan tewas masih dikonfirmasi.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614540/kemlu-3-abk-wni-diserang-rudal-houthi-di-selat-bab-al-mandeb</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/30/direktur-perlindungan-wni-kementerian-luar-negeri-kemlu-heni-hamidah-1777527020619_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Berapa Kali Sebaiknya Medical Check Up dalam Setahun? Ini Penjelasan Dokter</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 02:30:20 +0700</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Menurut Dokter Spesialis Patologi Klinik RS PKU Muhammadiyah Surakarta, dr. Hapsary Puteri,  seseorang disarankan melakukan MCU setahun sekali.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/kesehatan/7867147/berapa-kali-sebaiknya-medical-check-up-dalam-setahun-ini-penjelasan-dokter</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/h9Iwq3jQiUY5KGuceYOueGo4SFg=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ilustrasi-medical-check-up-istimewa-jk.jpg</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>5 Tempat Persembunyian Donald Trump: Terbaru di Dalam Truk Katering</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 02:02:21 +0700</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Trump beberapa kali harus disembunyikan demi keamanan, termasuk saat dipindahkan dengan truk katering bandara karena ancaman Iran</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7867146/5-tempat-persembunyian-donald-trump-terbaru-di-dalam-truk-katering</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/G_fSln9DwkqFdZKehzhyGyDgAgw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Donald-T1rump-melakukan-konferensi-si.jpg</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1 Juta Sarjana Menganggur, Pakar Soroti Ketidakseimbangan Jumlah Lulusan dan Daya Serap Pasar Kerja</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 01:20:16 +0700</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Menurut data pada Mei 2026, jumlah penduduk yang tidak bekerja sebanyak 7,22 juta orang, sekitar 14,31 persen di antaranya adalah lulusan sarjana.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867145/1-juta-sarjana-menganggur-pakar-soroti-ketidakseimbangan-jumlah-lulusan-dan-daya-serap-pasar-kerja</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/DPX12N-mX0CtRVfqOLpyiUHnrwE=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ilustrasi-peraih-gelar-sarjana-9.jpg</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Sistem Air di 12 Negara Bagian AS Diretas, Iran Dicurigai sebagai Dalang</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 01:03:29 +0700</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Serangan siber menyasar sistem air di sedikitnya tujuh negara bagian AS, termasuk lebih dari 30 sistem di Minnesota.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7867144/sistem-air-di-12-negara-bagian-as-diretas-iran-dicurigai-sebagai-dalang</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/-iLI2GIlawBLJIXGkQMMdQkM2aA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Tangkap-layar-YouTube-ABC-News-memperlihatkan-contoh-sistem-air-di-Am.jpg</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I20"/>
+  <autoFilter ref="A1:I27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-12.xlsx
+++ b/data/berita_2026-08-12.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,13 +419,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
@@ -1702,8 +1702,102 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Pabrik Bingkai di Duren Sawit Jaktim Kebakaran, 22 Unit Damkar Dikerahkan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 03:07:06 +0700</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Azhar Bagas Ramadhan</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Kebakaran melanda pabrik bingkai di Duren Sawit, Jakarta Timur. 100 personel damkar dikerahkan, namun terkendala akses dan sumber air. Penyebab belum diketahui.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614543/pabrik-bingkai-di-duren-sawit-jaktim-kebakaran-22-unit-damkar-dikerahkan</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/12/kebakaran-pabrik-bingkai-di-duren-sawit-jaktim-rabu-128-dini-hari-dok-istimewa-1786478796541_34.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Profil Nasaruddin Umar, Menteri Agama yang Berpeluang Jadi Calon Ketua Umum PBNU</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 03:02:11 +0700</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Menteri Agama K.H. Nasaruddin Umar disebut berpeluang maju menjadi calon Ketua Umum Pengurus Besar Nahdlatul Ulama (PBNU).</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867148/profil-nasaruddin-umar-menteri-agama-yang-berpeluang-jadi-calon-ketua-umum-pbnu</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/ZHG5-J1vu7NxJTscg7aMzkVoL3o=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Menteri-Agama-Nasaruddin-Umar-1111.jpg</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I27"/>
+  <autoFilter ref="A1:I29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-12.xlsx
+++ b/data/berita_2026-08-12.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1796,8 +1796,666 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Emery nilai melawan PSG  ujian bagus</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 04:14:16 +0700</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Pelatih Aston Villa Unai Emery menilai laga melawan Paris Saint-Germain (PSG) dalam  Piala Super Eropa di Stadion ...</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690147/emery-nilai-melawan-psg-ujian-bagus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/image-41.jpg</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PSG antusias sambut laga Piala Super lawan Aston Villa</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 04:08:18 +0700</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Pelatih Paris Saint-Germain (PSG) Luis Enrique mengatakan timnya antusiastis  menyambut laga Piala Super Eropa ...</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690145/psg-antusias-sambut-laga-piala-super-lawan-aston-villa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/1U6A2198_fgqcuq.jpg</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>DHL perkuat kesiapan kerja generasi muda lewat GoTeach dan UPGRADE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 04:04:36 +0700</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>DHL Group memperkuat kesiapan kerja generasi muda Indonesia melalui program GoTeach dan UPGRADE dengan menghadirkan ...</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690143/dhl-perkuat-kesiapan-kerja-generasi-muda-lewat-goteach-dan-upgrade</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/F9894DC9-42C3-46AD-BD3C-4AE394FBF07E.jpeg</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Al Ittihad dan Pakhtakor melangkah ke fase liga ACL Elite</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 04:02:03 +0700</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Al Ittihad dan Pakthtakor melangkah ke fase liga AFC Champions League (ACL) Elite wilayah barat setelah menyingkirkan ...</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690139/al-ittihad-dan-pakhtakor-melangkah-ke-fase-liga-acl-elite</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/image-40.jpg</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BMKG prakirakan sebagian besar Jakarta cerah di Rabu pagi</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 04:01:38 +0700</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) memprakirakan sebagian besar wilayah DKI Jakarta dalam kondisi ...</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690136/bmkg-prakirakan-sebagian-besar-jakarta-cerah-di-rabu-pagi</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/19/IMG_20260719_000858.jpg</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Pengamat nilai insentif diperlukan untuk wujudkan zero ODOL di 2027</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 03:57:59 +0700</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Pengamat transportasi dari Inisiasi Strategis Transportasi (Instran) Deddy Herlambang menilai insentif diperlukan untuk ...</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690135/pengamat-nilai-insentif-diperlukan-untuk-wujudkan-zero-odol-di-2027</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/E2F5FB05-5F99-4113-A031-16C9D172E36C.jpeg</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Bardghji terancam absen bela Barcelona karena operasi ligamen</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 03:55:44 +0700</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Gelandang Barcelona Roony Bardghji terancam absen membela Blaugrana karena harus menjalani operasi ligamen pada lutut ...</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690131/bardghji-terancam-absen-bela-barcelona-karena-operasi-ligamen</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/05/16/FCB.jpg</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Pelindo Multi Terminal: Arus barang capai 59,59 juta ton di semester I</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 03:54:24 +0700</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>PT Pelindo Multi Terminal, anak usaha PT Pelabuhan Indonesia (Persero), mencatat arus barang mencapai 59,59 juta ton ...</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690127/pelindo-multi-terminal-arus-barang-capai-5959-juta-ton-di-semester-i</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/897B7F64-B5C0-43BC-9080-8B0E7FEFDA55.jpeg</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Bayi Dikubur di Rumah Pasutri Mojokerto Ternyata Korban Pembunuhan</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 04:14:29 +0700</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Enggran Eko Budianto</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Kuburan bayi ditemukan di rumah pasutri Mojokerto. Autopsi mengungkap bayi dibunuh setelah lahir, meninggal karena dibekap. Investigasi masih berlanjut.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614548/bayi-dikubur-di-rumah-pasutri-mojokerto-ternyata-korban-pembunuhan</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/pemakaman-bayi-yang-sempat-dikubur-di-rumah-warga-mojokerto-1786443183049_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Hanura Usul Sistem Pemilu 2029 Gabungkan Proporsional Terbuka-Tertutup</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 03:41:06 +0700</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Alamudin Hamapu</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Partai Hanura usulkan sistem pemilu 2029 gabungkan proporsional terbuka dan tertutup. Tujuannya, tingkatkan kualitas anggota DPR dan DPRD.</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614546/hanura-usul-sistem-pemilu-2029-gabungkan-proporsional-terbuka-tertutup</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/10/ketua-tim-task-force-hanura-patrice-rio-cappella-di-medan-nizar-aldidetiksumut-1786378134569_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Prakiraan Cuaca Banyumas, Rabu 12 Agustus 2026: Mayoritas Daerah Cerah</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 04:12:22 +0700</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Pada hari Rabu, 12 Agustus 2026, sebagian besar daerah Kabupaten Banyumas, Jawa Tengah, akan cerah.</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7867151/prakiraan-cuaca-banyumas-rabu-12-agustus-2026-mayoritas-daerah-cerah</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/AX_5QI3DZO6kl9mzAYeoSUl6g3A=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Foto-ilustrasi-cuaca-cerah-berawan-ilustrasi-cerah-berawan.jpg</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>20 Link Twibbon Hari Gajah Sedunia 2026, Lengkap dengan Cara Mudah Unggah di Media Sosial</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 04:06:56 +0700</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Link Twibbon Hari Gajah Sedunia 2026, bingkai foto cocok dipakai sebagai foto profil dan diunggah di sosial media pada tanggal 12 Agustus 2026.</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867150/20-link-twibbon-hari-gajah-sedunia-2026-lengkap-dengan-cara-mudah-unggah-di-media-sosial</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/PrguIH4HcnLzDzgSnyAolmMdrJU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Link-Twibbon-Hari-Gajah-Sedunia-2026-bingkai-foto.jpg</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Pertumbuhan Ekonomi RI 5,29 Persen, Ferry Latuhihin: Tinggi, tapi Gagal Ciptakan Lapangan Kerja</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 03:33:38 +0700</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Ferry Latuhihin menyebut di Indonesia terjadi immiserizing growth atau pertumbuhan yang justru memiskinkan rakyat.</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867149/pertumbuhan-ekonomi-ri-529-persen-ferry-latuhihin-tinggi-tapi-gagal-ciptakan-lapangan-kerja</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/y096sh1ukVa6j3okWpbaC5lOJ1c=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Konferensi-pers-Badan-Pusat-Statistik-mengenai-pertumbuhan-ekonomi.jpg</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Cuaca Jakarta Rabu Diprediksi Cerah, Suhu Capai 35 Derajat</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 04:28:13 +0700</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>BMKG memprakirakan cuaca Jakarta didominasi cerah dan cerah berawan sepanjang Rabu dengan suhu mencapai 35 derajat Celsius.</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267588/cuaca-jakarta-rabu-diprediksi-cerah-suhu-capai-35-derajat</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/3-F2plV7Pg7xWbP2yDN5g6R05rM=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/3453943/original/049969200_1620650232-Jakarta_Cerah.jpg</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I29"/>
+  <autoFilter ref="A1:I43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-12.xlsx
+++ b/data/berita_2026-08-12.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,18 +419,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2454,8 +2454,572 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Empat kementerian/lembaga sepakat satu data tangani korban Napza</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 05:15:40 +0700</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ANTARA - Kementerian Sosial, Kementerian Kesehatan, Kementerian Ketenagakerjaan, dan Badan Narkotika Nasional ...</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5690124/empat-kementerian-lembaga-sepakat-satu-data-tangani-korban-napza</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/EMPAT-KEMENTERIANLEMBAGA-SEPAKAT-SATU-DATA-TANGANI-KORBAN-NAPZA.jpg</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Konser Kemerdekaan GBN 2026 digelar perdana di Bogor</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 05:09:38 +0700</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>ANTARA - Konser Kemerdekaan Gita Bahana Nusantara (GBN) 2026 digelar untuk pertama kalinya di Kabupaten Bogor, tepatnya ...</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5690121/konser-kemerdekaan-gbn-2026-digelar-perdana-di-bogor</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/KONSER-KEMERDEKAAN-GBN-2026-DIGELAR-PERDANA-DI-BOGOR.jpg</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Ekshumasi Jasad Sutrismo Digelar Hari Ini, Keluarga Tak Hadir</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 05:08:36 +0700</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Anang Firmansyah</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Ekshumasi jenazah Sutrimo di Banyumas digelar hari ini tanpa kehadiran keluarga. Kuasa hukum memastikan keluarga siap dan menyerahkan proses kepada hukum.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614557/ekshumasi-jasad-sutrismo-digelar-hari-ini-keluarga-tak-hadir</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/suasana-makam-sutrimo-jelang-ekshumasi-di-desa-wlahar-kecamatan-wangon-kabupaten-banyumas-selasa-1182026-1786435403861_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Nabilah Rahman Dozan Jadi Ibu, Perlihatkan Momen Melahirkan</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 05:05:45 +0700</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Ada kabar bahagia dari kreator Nabilah Rahman Dozan. Anak Betharia Sonata-Willy Dozan itu telah menjadi ibu.</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8614365/nabilah-rahman-dozan-jadi-ibu-perlihatkan-momen-melahirkan</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/nabilah-rahman-dozan-1786456492508_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>FOTO: Topan Dolphin Bikin Shanghai Kebanjiran</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 04:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Topan Dolphin membanjiri sejumlah kawasan di Shanghai, China, pada Senin (10/8).</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260810162823-115-1390688/foto-topan-dolphin-bikin-shanghai-kebanjiran</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/10/topan-dolphin-bikin-shanghai-kebanjiran-1786354080836_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Evakuasi Longsor Imbas Hujan Deras di Baguio Filipina, 10 Orang Tewas</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 03:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Sebanyak 10 orang tewas akibat tanah longsor yang dipicu hujan deras dan banjir di kota Baguio, Filipina utara.</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260811143515-110-1391034/evakuasi-longsor-imbas-hujan-deras-di-baguio-filipina-10-orang-tewas</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/11/thumbnail-video-1786433847390_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Respons Lisa Mariana saat Namanya Kembali Dikaitkan dalam Kasus Ridwan Kamil</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 05:04:08 +0700</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Selebgram Lisa Mariana memberikan respons saat namanya kembali dikaitkan dalam kasus Ridwan Kamil.</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7867152/respons-lisa-mariana-saat-namanya-kembali-dikaitkan-dalam-kasus-ridwan-kamil</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/s1l79hkTpSazeGfRNRx-CThSk6w=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Lisa-Mariana-Jalani-Pemeriksaan-Sebagai-Tersangka_20251025_072830.jpg</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Otomotif</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>New Xforce HEV, Strategi Mitsubishi Hadirkan Hybrid Sebagai Pilihan yang Lebih Irit</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 04:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Israr Itah</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, TANGERANG -- Bagi sebagian orang, daya tarik sebuah mobil bukan sekadar tampilan atau banyaknya fitur. Seberapa sering harus berhenti di SPBU, berapa besar biaya yang perlu disiapkan setiap bulan,...</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjm90z348/new-xforce-hev-strategi-mitsubishi-hadirkan-hybrid-sebagai-pilihan-yang-lebih-irit</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/037938500-1785556282-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Kebakaran di Bromo Belum Padam, 2 Titik Api Tersisa di Tebing Curam</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 05:21:30 +0700</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>​ BNPB Targetkan Karhutlah di Gunung Bromo pad Total Akhir Pekan ini</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267597/kebakaran-di-bromo-belum-padam-2-titik-api-tersisa-di-tebing-curam</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/voWV0fDTfAVK22PREFRzLVP6ees=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321678/original/005690100_1786486848-IMG-20260809-WA0038_copy_1024x683_1.jpg</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Cerita Pilu dari Atas Jalur Kereta Jurangmangu</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 05:11:39 +0700</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Kasus siswi tertemper kereta di Stasiun Jurangmangu masih menjadi misteri.</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267576/cerita-pilu-dari-atas-jalur-kereta-jurangmangu</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/wsCOKo7lwpcHFOmpQEe6udxnRi4=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9320985/original/089880800_1786422102-318f8b17-947b-4bbd-b67a-057361f46779.jpg</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Situs Sejarah Bogor Naik Status Cagar Budaya Nasional, Ini Daftarnya</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 04:41:31 +0700</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Kemenbud menyiapkan sejumlah situs bersejarah di Kabupaten Bogor untuk direvitalisasi dan ditingkatkan statusnya menjadi Cagar Budaya Nasional.</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267590/situs-sejarah-bogor-naik-status-cagar-budaya-nasional-ini-daftarnya</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/XKMPbLLXaZ_sGEi7RpoTddXobWU=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321673/original/004543500_1786484142-1003331109.jpg</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Jaksa Beberkan 27 Nama Penerima Uang dari Kasus Korupsi Kuota Haji Khusus</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 04:43:18 +0700</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Angka yang mengalir ribuan hingga hingga jutaan dolar Amerika Serikat.</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267091/jaksa-beberkan-27-nama-penerima-uang-dari-kasus-korupsi-kuota-haji-khusus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/Kcc9tinbWO-BlcvrzhwjP66t9xo=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321231/original/009653200_1786434165-IMG_20260811_135837_642.jpg</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I43"/>
+  <autoFilter ref="A1:I55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-12.xlsx
+++ b/data/berita_2026-08-12.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3018,8 +3018,1230 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BNN usulkan tim terpadu awasi tempat rehabilitasi narkotika</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 06:26:42 +0700</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Badan Narkotika Nasional (BNN) mengusulkan pembentukan tim terpadu lintas instansi untuk memperkuat pengawasan terhadap ...</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690156/bnn-usulkan-tim-terpadu-awasi-tempat-rehabilitasi-narkotika</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/1003331133.jpg</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Gedung Biro Kesra Setda Kantor Gubernur Kalteng terbakar</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 06:17:10 +0700</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Gedung yang digunakan sebagai Biro Kesejahteraan Rakyat (Kesra) Sekretariat Daerah (Setda) Provinsi Kalimantan Tengah ...</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690153/gedung-biro-kesra-setda-kantor-gubernur-kalteng-terbakar</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/1001742010.jpg</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>JPU: Pengaturan kuota haji tambahan "satu pintu" lewat Fuad Hasan</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 06:05:05 +0700</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Jaksa Penuntut Umum (JPU) dari Komisi Pemberantasan Korupsi (KPK) Fahmi Idris menyebut pengaturan pengisian kuota haji ...</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690151/jpu-pengaturan-kuota-haji-tambahan-satu-pintu-lewat-fuad-hasan</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/18/KPK-periksa-Fuad-Hasan-Masyhur-terkait-korupsi-penyelenggaraan-haji-180626-sth-01A.jpg</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Siaga jaga keamanan acara HUT ke-81 RI</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 06:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Pengamanan intensif disiapkan guna memastikan seluruh rangkaian acara HUT ke-81 RI di Jakarta berjalan lancar. ...</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/infografik/5689489/siaga-jaga-keamanan-acara-hut-ke-81-ri</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/20260811-Siaga-jaga-keamanan-acara-HUT-ke-81-RI.jpg</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Deras Kecaman Challenge Hafal Al-Qur'an Berhadiah Miras</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 06:04:39 +0700</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Tim detikcom</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Aksi tantangan promosi miras berkedok tantangan hafalan Al-Qur'an viral di media sosial. Tindakan itu mendapatkan respons keras berbagai kalangan masyarakat</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614571/deras-kecaman-challenge-hafal-al-quran-berhadiah-miras</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/1144667396-1786419072166_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Pendaftaran Magang Nasional Batch 2 Dibuka Bulan Depan</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 05:55:44 +0700</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Program magang nasional batch 2 tahun 2026 akan dibuka pertengahan September atau bulan depan.</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8613927/pendaftaran-magang-nasional-batch-2-dibuka-bulan-depan</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/06/14/gedung-kemnaker_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Lucky Girl! Potret Gempita Nora Marten Jadi Player Escort AC Milan</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 06:03:40 +0700</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Gading Marten baru mengunggah momen Gempita menjadi player escort AC Milan dalam laga lawan Chelsea di GBK. Wah... kesempatan yang langka banget ya Gem!</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8614564/lucky-girl-potret-gempita-nora-marten-jadi-player-escort-ac-milan</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/12/gempita-nora-marten-1786473042713_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>BWF Soroti 5 Ganda Putri Kandidat Juara di Kejuaraan Dunia BWF 2026, China Masih Dominan</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 06:10:45 +0700</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>BWF menyoroti lima pasangan ganda putri yang berpeluang kuat memperebutkan gelar juara Kejuaraan Dunia BWF 2026 di New Delhi.</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7867166/bwf-soroti-5-ganda-putri-kandidat-juara-di-kejuaraan-dunia-bwf-2026-china-masih-dominan</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/FVpXNnAKNHPDJwLvMjAxW68URys=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/pasangan-baek-ha-na-dan-lee-so-he-juara-ganda-putri-indonesia-open-2024_20240609_162819.jpg</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Waspada Dokter AI di YouTube dan TikTok, Lansia Jadi Target karena Mudah Percaya Klaim Sembuh Instan</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 06:05:05 +0700</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Fenomena "dokter AI" kini menjadi perhatian karena kecerdasan buatan dapat dimanfaatkan untuk membuat akun yang tampak seperti akun dokter.</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/kesehatan/7867165/waspada-dokter-ai-di-youtube-dan-tiktok-lansia-jadi-target-karena-mudah-percaya-klaim-sembuh-instan</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/B2znGZiLatFc4eBlvPbS53WlfhY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ilustrasi-dokter-675755.jpg</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Sengketa Upah Berlanjut, Pekerja Hyundai Motor Akan Mogok Kerja Parsial 4 hari</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 06:01:27 +0700</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Serikat pekerja Hyundai Motor akan menggelar aksi mogok kerja parsial 4 hari minggu ini setelah gagal mencapai kesepakatan soal upah dengan manajemen.</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/otomotif/7867164/sengketa-upah-berlanjutpekerja-hyundai-motor-akan-mogok-kerja-parsial-4-hari</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/wq63QilbG0SiqNAeGylSS7wVfxo=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Preskon-Serikat-Pekerja-Hyundai.jpg</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Senpi Dipakai Mantan Istri hingga Tewas, Brigadir Imansyah Dipatsus</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 05:58:05 +0700</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Iman bukan ditahan karena tindak pidana pembunuhan mantan istri, melainkan dugaan kelalaian senjata apinya digunakan Winda untuk dugaan bunuh diri.</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7867163/senpi-dipakai-mantan-istri-hingga-tewas-brigadir-imansyah-dipatsus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/tCmUGnrMn3EXKOVRe3-h9sRQHRI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Winda-Lorenza-Gowasa-ditemukan-meninggal.jpg</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Hasil 10 Laga Awal Man City Masih Misteri, Pep Guardiola Bikin Enzo Maresca Sadar Posisi</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 05:57:56 +0700</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Enzo Maresca sadar bayang-bayang Pep Guardiola akan selalu mengikutinya di Manchester City. Namun, dia merasa terhormat.</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7867162/hasil-10-laga-awal-man-city-masih-misteri-pep-guardiola-bikin-enzo-maresca-sadar-posisi</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/vfDR7WH13Yq2TymeJufIk9xRI6o=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Enzo-Maresca-Chelsea-412.jpg</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Challenge Hafalan Surat Ad-Dhuha Berhadiah Miras Viral, Ahli Hukum: Polisi Bisa Langsung Bertindak</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 05:46:34 +0700</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Dugaan penistaan agama melalui challenge hafalan Surat Ad-Dhuha dengan imbalan minuman keras (miras) di sebuah festival musik menjadi sorotan.</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7867161/challenge-hafalan-surat-ad-dhuha-berhadiah-miras-viral-ahli-hukum-polisi-bisa-langsung-bertindak</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/uZeNIDQRbmXfRPd3jGtgCkapzCg=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Abdul-Fickar-Hadjar-Pakar-Hukum-Pidana-1.jpg</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Terjemahan Lirik Lagu She's The One - Robbie Williams: I was Her, She was Me, We were One</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 05:43:50 +0700</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Simak terjemahan lirik lagu "She's The One" yang pernah dibawakan oleh penyanyi sekaligus penulis lagu asal Inggris, Robbie Williams.</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/musik/7867160/terjemahan-lirik-lagu-shes-the-one-robbie-williams-i-was-her-she-was-me-we-were-one</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/dizVB9x6SK7BSsXjPU6kpy9COv4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/headset-vd-pink.jpg</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>5 Populer Internasional: Gempa M7,4 di Kolombia - Festival Indonesia di Jepang Berakhir Ricuh</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 05:43:15 +0700</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Gempa magnitudo 7,4 mengguncang Kolombia, menewaskan 110 orang, melukai puluhan, dan lebih dari 1.400 laporan orang hilang masuk.</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7867159/5-populer-internasional-gempa-m74-di-kolombia-festival-indonesia-di-jepang-berakhir-ricuh</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/hzWx5otJiYfuvi7E1WBaYnCcYqs=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/KONDISI-KOTA-PEREIRA-SETELAH-GEMPA-GUNCANG-KOLOMBIA.jpg</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Sosok Rico Roberto Syah, Pemuda Beri Mahar Eskavator ke Istri saat Nikah, Anak Kades di Grobogan</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 05:39:23 +0700</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Rico viral usai memberi mahar ekskavator dan mobil mewah senilai miliaran rupiah, ternyata anak kepala desa dan pengusaha alat berat.</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7867158/sosok-rico-roberto-syah-pemuda-beri-mahar-eskavator-ke-istri-saat-nikah-anak-kades-di-grobogan</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Lk5EsQgM-2vRsI5Pcqs_dGtaHEY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/P-Sosok-Rico-Roberto-Syah-Pemuda-Beri-Mahar-Eskavator-ke-Istri-saat-Nikah-Anak-Kades-di-Grobogan.jpg</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Wardatina Mawa Ungkap Cara Co-parenting Bersama Insanul Fahmi setelah Resmi Cerai</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 05:36:38 +0700</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Meski telah resmi berpisah, konten kreator Wardatina Mawa tetap jalani co-parenting bersama Insanul Fahmi.</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7867157/wardatina-mawa-ungkap-cara-co-parenting-bersama-insanul-fahmi-setelah-resmi-cerai</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/ErCYTFkO3XgNmOrc7eBO-8wiYgM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Wardatina-Mawa-menunjukkan-tanda-bukti-laporan-kepolisian-perselingkuhan-Inara-Rusli.jpg</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Hasil Kualifikasi Liga Champions Tadi Malam: Eks Klub Calvin Verdonk Menang, Penakluk Inter Menggila</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 05:25:31 +0700</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Drama Kualifikasi Liga Champions 2026/2027! Eks klub Calvin Verdonk, NEC Nijmegen, sukses menyingkirkan Olympiakos, dan kini menuju rekor bersejarah.</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7867156/hasil-kualifikasi-liga-champions-tadi-malam-eks-klub-calvin-verdonk-menang-penakluk-inter-menggila</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/u5hoK4C9GH03Myg2wW1vEVD9QQs=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/gambar-ini-menunjukkan-trofi-liga-champions-uefa-sebelum-pengundian.jpg</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Prakiraan Cuaca Sulawesi Barat Rabu, 12 Agustus 2026: Mamuju Cerah</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 05:23:46 +0700</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>BMKG melaporkan prakiraan cuaca untuk wilayah Sulawesi Barat (Sulbar), Rabu (12/8/2026). Mamuju akan cerah hari ini.</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7867155/prakiraan-cuaca-sulawesi-barat-rabu-12-agustus-2026-mamuju-cerah</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/b6l4ZqXyMCa4bjxdlZtvFOJ6Lbs=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Prakiraan-Cuaca-Sulawesi-Barat.jpg</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>5 Populer Regional: Sosok PPPK Live Medsos saat Jam Kerja - KH Anwar Zahid Alami Kecelakaan</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 05:22:20 +0700</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>PPPK Bandung Barat viral bahas dugaan fee proyek 1 persen saat jam kerja, sementara mobil KH Anwar Zahid ditabrak truk di Bojonegoro.</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7867154/5-populer-regional-sosok-pppk-live-medsos-saat-jam-kerja-kh-anwar-zahid-alami-kecelakaan</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Pb-TMS02knqut0jv5amkSddVkvU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Indah-Live-TikTok.jpg</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Trump Diam-diam Dipindah dari Air Force One Pakai Truk Katering demi Hindari Ancaman Iran</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 05:18:04 +0700</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Trump diam-diam dipindahkan dari Air Force One lewat truk katering ke jet militer setelah muncul ancaman pembunuhan dari Iran.</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7867153/trump-diam-diam-dipindah-dari-air-force-one-pakai-truk-katering-demi-hindari-ancaman-iran</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Ft6MFHVX9_dtn4yZZXYEToZRi-Y=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/AIR-FORCE-ONE-Tangkap-layar-YouTube-Associated-Press-2-J.jpg</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Mahasiswa Riset SPPG, Dampak ke UMKM dan Ekonomi Lokal Dikaji</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 06:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Satria K Yudha</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA – Pelaksanaan Satuan Pelayanan Pemenuhan Gizi (SPPG) tidak hanya berkaitan dengan pemenuhan gizi penerima manfaat, tetapi juga memiliki dampak terhadap aktivitas ekonomi di sekitar dapur. Penyerapan UMKM sebagai...</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjm29u416/mahasiswa-riset-sppg-dampak-ke-umkm-dan-ekonomi-lokal-dikaji</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/047822600-1775755284-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Otomotif</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>New Xforce HEV, Strategi Mitsubishi Hadirkan Hybrid Sebagai Pilihan yang Lebih Ekonomis</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 04:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Israr Itah</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, TANGERANG -- Bagi sebagian orang, daya tarik sebuah mobil bukan sekadar tampilan atau banyaknya fitur. Seberapa sering harus berhenti di SPBU, berapa besar biaya yang perlu disiapkan setiap bulan,...</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjm90z348/new-xforce-hev-strategi-mitsubishi-hadirkan-hybrid-sebagai-pilihan-yang-lebih-ekonomis</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/037938500-1785556282-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Seleksi Hakim Agung, KY Ungkap Hal yang Bikin Identitas Calon Tersembunyi</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 06:16:20 +0700</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>KY memastikan seleksi calon hakim agung dan hakim ad hoc 2026 berlangsung transparan dengan melibatkan publik dan menerapkan mekanisme blind review.</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267613/seleksi-hakim-agung-ky-ungkap-hal-yang-bikin-identitas-calon-tersembunyi</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/SOZ0nfn8RgmbOySv6A3U2HW6IiM=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/1102777/original/054688000_1452067414-20160106--Ilustrasi-Gedung-Komisi-Yudisial-Hel2.jpg</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Ketika Agama Dibuat Challenge Berhadiah Miras, Tak Ada Alasan Ampuni Pelaku</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 06:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Sebuah tantangan di tengah riuh festival musik The Sounds Project di kawasan Ancol mendadak berubah menjadi polemik.</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267575/ketika-agama-dibuat-challenge-berhadiah-miras-tak-ada-alasan-ampuni-pelaku</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/Fp5iC-vppn7dJSzwqGEBlrLz0gY=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321055/original/059736500_1786425649-Jepretan_Layar_2025-08-11_pukul_12.15.34.jpg</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Pesan Megawati untuk Pimpinan Organisasi Sayap Partai</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 05:53:56 +0700</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Megawati Soekarnoputri melantik pimpinan organisasi sayap PDIP, meminta kader dekat dengan rakyat. Ia juga menyoroti masalah sarjana menganggur dan menugaskan badan riset mencari solusi.</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267610/pesan-megawati-untuk-pimpinan-organisasi-sayap-partai</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/m48HfJYPaJEZKeA4JZOFEYcJ3b0=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321561/original/095047900_1786449805-DSC02530.jpg.jpeg</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I55"/>
+  <autoFilter ref="A1:I81"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-12.xlsx
+++ b/data/berita_2026-08-12.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$133</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,13 +419,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="43" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
@@ -4240,8 +4240,2453 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Top News</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Rabu, BMKG: Mayoritas kota besar alami berawan-hujan ringan</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:17:53 +0700</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) mengeluarkan peringatan dini berupa potensi hujan ringan, sedang ...</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690181/rabu-bmkg-mayoritas-kota-besar-alami-berawan-hujan-ringan</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/08/304062.jpg</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Top News</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>DKI beri sanksi Rp10 juta kepada penyedia jasa angkut sampah nakal</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:08:50 +0700</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi (Pemprov) DKI Jakarta memberikan sanksi administratif Rp10 juta serta teguran tertulis pertama ...</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690172/dki-beri-sanksi-rp10-juta-kepada-penyedia-jasa-angkut-sampah-nakal</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/1000319700.jpg</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Top News</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Kemnaker siapkan akses pelatihan-peluang kerja bagi penyintas narkoba</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 06:57:49 +0700</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Kementerian Ketenagakerjaan (Kemnaker) menyiapkan akses pelatihan dan peluang atau kesempatan kerja bagi penyintas ...</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690168/kemnaker-siapkan-akses-pelatihan-peluang-kerja-bagi-penyintas-narkoba</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/IMG_0820.jpeg</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Top News</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Gedung Biro Kesra Setda Provinsi Kalteng terbakar</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 06:17:10 +0700</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Gedung yang digunakan sebagai Biro Kesejahteraan Rakyat (Kesra) Sekretariat Daerah (Setda) Provinsi Kalimantan Tengah ...</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690153/gedung-biro-kesra-setda-provinsi-kalteng-terbakar</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/1001742010.jpg</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Cara klaim asuransi mobil: Syarat, dokumen, dan prosedurnya</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:53:35 +0700</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/antaranewsdotcom</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Mengajukan klaim asuransi mobil membutuhkan kelengkapan dokumen dan ketepatan mengikuti prosedur yang ditetapkan ...</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5690216/cara-klaim-asuransi-mobil-syarat-dokumen-dan-prosedurnya</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2017/02/20170201antarafoto-asuransi-astra-310117-ho.jpg</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Biaya klaim asuransi mobil berapa? Ini rincian dan contohnya</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:50:53 +0700</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/antaranewsdotcom</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Biaya klaim asuransi mobil tidak selalu sepenuhnya ditanggung perusahaan asuransi. Pemilik kendaraan umumnya tetap ...</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5690211/biaya-klaim-asuransi-mobil-berapa-ini-rincian-dan-contohnya</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2022/02/03/IMG-20220203-WA0036.jpg</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Politik</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Paskibra vs Paskibraka: Ini perbedaan dan tugasnya</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:41:01 +0700</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Paskibra dan Paskibraka sama-sama berkaitan dengan tugas pengibaran bendera Merah Putih. Namun, keduanya memiliki ...</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690197/paskibra-vs-paskibraka-ini-perbedaan-dan-tugasnya</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/09/latihan-paskibraka-di-sulawesi-barat-2837643.jpg</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Politik</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Formasi 17-8-45 Paskibraka: Sejarah dan makna di baliknya</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:37:14 +0700</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Formasi 17-8-45 menjadi bagian penting dalam pelaksanaan tugas Pasukan Pengibar Bendera Pusaka (Paskibraka) pada ...</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690195/formasi-17-8-45-paskibraka-sejarah-dan-makna-di-baliknya</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/10/1003327208.jpg</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Karhutla Belum Padam, Penutupan Bromo Diperpanjang hingga 15 Agustus</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:29:36 +0700</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Muhammad Aminudin</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Kebakaran hutan di Gunung Bromo masih berlangsung, akses wisata ditutup hingga 15 Agustus 2026. Wisatawan dapat mengajukan refund atau reschedule tiket.</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614598/karhutla-belum-padam-penutupan-bromo-diperpanjang-hingga-15-agustus</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/09/11/belum-padam-gunung-bromo-hangus-dilalap-api-3_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Ternyata Dedi Congor Sudah Jadi Tersangka</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:03:51 +0700</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Tim deticom</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Dedi juga terjerat kasus gratifikasi yang kasusnya diselidiki kepolisian sejak 2023.</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614589/ternyata-dedi-congor-sudah-jadi-tersangka</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/08/pns-bea-cukai-ahmad-dedi-ad-lari-usai-diperiksa-kpk-demi-menghindari-wartawan-adrial-akbardetikcom-1778241473937_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Media Malaysia Soroti Asap Karhutla di Kalimantan Terbawa ke Sarawak</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 06:53:47 +0700</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Azhar Bagas Ramadhan</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Media Malaysia melaporkan kualitas udara memburuk akibat kabut asap dari Kalimantan. Sepuluh wilayah di Malaysia, terutama Sarawak.</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614585/media-malaysia-soroti-asap-karhutla-di-kalimantan-terbawa-ke-sarawak</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/ratusan-titik-panas-terdeteksi-karhutla-ancam-sejumlah-wilayah-kalbar-1785728076376_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Terungkap Negara Rugi Rp 622 M saat Yaqut Didakwa Kasus Kuota Haji</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 06:30:55 +0700</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Tim detikcom</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Mantan Menag Yaqut Cholil Qoumas didakwa korupsi kuota haji 2023-2024, merugikan negara Rp 622 miliar. Jaksa ungkap detail kerugian dan keterlibatan pihak lain.</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614578/terungkap-negara-rugi-rp-622-m-saat-yaqut-didakwa-kasus-kuota-haji</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/eks-menag-yaqut-didakwa-perkara-kuota-haji-negara-disebut-rugi-rp622-miliar-1786428544180_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Rencana Pemerintah Batasi Pertalite buat Orang Kaya</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:30:49 +0700</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Pemerintah berencana memperketat pembelian bahan bakar minyak (BBM) Pertalite.</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8614581/rencana-pemerintah-batasi-pertalite-buat-orang-kaya</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2015/07/27/a1dfc702-9caf-415e-aa20-a367dad1b9dc_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Pernak-pernik HUT RI Jadi Ladang Cuan Pedagang Musiman di Pasar Minggu</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Gilang Faturahman</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Menjelang HUT ke-81 RI, pedagang musiman ramai menjajakan pernak-pernik kemerdekaan. Beragam atribut merah putih dijual dengan harga bervariasi.</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/foto-bisnis/d-8614389/pernak-pernik-hut-ri-jadi-ladang-cuan-pedagang-musiman-di-pasar-minggu</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/pernak-pernik-hut-ri-jadi-ladang-cuan-pedagang-musiman-di-pasar-minggu-1786457391316.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Ada Aturan Baru, Driver Ojol Dijamin Tetap Dapat BHR</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 06:30:48 +0700</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Herdi Alif Al Hikam</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Driver ojek online (ojol) akan tetap mendapatkan bonus hari raya (BHR) Lebaran meskipun statusnya berubah jadi pengusaha mikro.</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8614576/ada-aturan-baru-driver-ojol-dijamin-tetap-dapat-bhr</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/11/10/ilustrasi-driver-ojol-1762782634885_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Congrats! Cristiano Ronaldo Menikahi Georgina Setelah 10 Tahun</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 06:57:53 +0700</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Cristiano Ronaldo menikahi Georgina Rodriguez setelah 10 tahun bersama. Pernikahan berlangsung intim di Cascais, Portugal, dihadiri kelima anak mereka.</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8614587/congrats-cristiano-ronaldo-menikahi-georgina-setelah-10-tahun</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/04/13/cristiana-ronaldo-dan-georgina-rodriguez-1744546792458_169.webp?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Netanyahu Ogah Ikut Trump, Seberapa Kuat Israel Serang Iran Sendirian?</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:35:25 +0700</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Israel dilaporkan sedang mempersiapkan kemungkinan melakukan serangan sepihak ke Iran jika perang Washington vs Teheran berakhir.</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260811203247-120-1391215/netanyahu-ogah-ikut-trump-seberapa-kuat-israel-serang-iran-sendirian</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/09/28/benjamin-netanyahu-1759026599434_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Malaysia Kirim Penyidik ke RI, Gali Informasi Kasus Pilot Bawa Narkoba</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:07:42 +0700</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Empat petugas Departemen Investigasi Kejahatan Narkotika Malaysia tiba di Jakarta, untuk mengusut kasus pilot yang kedapatan menyelundupkan narkoba ke RI.</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260812065631-106-1391260/malaysia-kirim-penyidik-ke-ri-gali-informasi-kasus-pilot-bawa-narkoba</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/03/14/ilustrasi-bendera-malaysia_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Trump Diam-diam Ganti Pesawat sampai Vonis Mati Bashar Al Assad</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 06:31:37 +0700</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Trump disebut ganti pesawat dari Air Force One ke pesawat kecil karena diancam dibunuh sampai Bashar Al Assad divonis mati.</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260812062514-134-1391255/trump-diam-diam-ganti-pesawat-sampai-vonis-mati-bashar-al-assad</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/03/22/presiden-as-donald-trump-1774175276156_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Satu WNI Dikabarkan Tewas Kena Serangan Houthi, Kemlu RI Buka Suara</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 06:00:42 +0700</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Kemlu RI disebut masih dalam proses verifikasi informasi soal satu ABK WNI yang dikabarkan tewas kena serangan Houthi di Yaman.</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260812055450-120-1391249/satu-wni-dikabarkan-tewas-kena-serangan-houthi-kemlu-ri-buka-suara</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2018/04/19/842fe7c6-b37b-4e52-8f34-3eb722ad1ed3_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Ini Menantu Sultan Brunei yang Pernah Viral</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 05:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Menantu Sultan Brunei Darussalam Sultan Bolkiah, Robiatul Adawiyyah, menjadi sorotan usai gelar kerajaan dicopot karena tindakan yang dianggap tak senonoh.</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260811190010-106-1391186/ini-menantu-sultan-brunei-yang-pernah-viral</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/01/15/akad-nikah-pangeran-abdul-mateen-dan-anisha-rosnah_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>KAI Tebar Promo Spesial 17 Agustus 2026, Tiket Kereta Diskon 17 Persen dan Tarif KRL-LRT Rp8</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:45:52 +0700</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>KAI beri promo spesial 17 Agustus 2026 berupa diskon 17 persen untuk KA Jarak Jauh kelas ekonomi komersial dan tarif Rp8 untuk KRL-LRT Jabodetabek.</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7867190/kai-tebar-promo-spesial-17-agustus-2026-tiket-kereta-diskon-17-persen-dan-tarif-krl-lrt-rp8</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/l4jTIvYBS-FFEYFIp7YKBVkJAZk=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Daftar-Kereta-Api-yang-Punya-Tarif-Khusus-di-Rute-Jogja-Solo.jpg</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Prakiraan Cuaca Yogyakarta, Rabu 12 Agustus 2026, BMKG: Didominasi Cerah</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:43:30 +0700</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Berikut prakiraan cuaca di  Provinsi Yogyakarta pada Rabu (12/8/2026). Menurut BMKG, mayoritas wilayah di Yogyakarta cuacanya akan cerah.</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7867189/prakiraan-cuaca-yogyakarta-rabu-12-agustus-2026-bmkg-didominasi-cerah</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/_NtT6j7i5suz6vLyHHQ1z3sEhbQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Pemandangan-kawasan-Tugu-Pal-Putih-Yogyakarta.jpg</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Prakiraan Cuaca Jabodetabek Rabu, 12 Agustus 2026: Jakarta, Depok, Tangerang, dan Bekasi Cerah</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:42:45 +0700</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>BMKG memprakirakan wilayah Jakarta, Depok, Tangerang, dan Bekasi akan cerah hari ini, Rabu (12/8/2026). Sementara Bogor diprediksi berawan.</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7867188/prakiraan-cuaca-jabodetabek-rabu-12-agustus-2026-jakarta-depok-tangerang-dan-bekasi-cerah</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Ew22ZWpIXWs0i0Fg5jOcsd0PKDk=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/cuaca-cerah-sekali.jpg</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Daftar 14 Kantor hingga Mobil di Pemkab Puncak Papua Tengah Dibakar Massa Usai Penyaluran Dana Desa</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:41:30 +0700</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Sejumlah fasilitas kantor Pemerintahan Kabupaten Puncak, Papua Tengah dibakar massa usai penyaluran Dana Desa (DD) tahap pertama reguler.</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7867187/daftar-14-kantor-hingga-mobil-di-pemkab-puncak-papua-tengah-dibakar-massa-usai-penyaluran-dana-desa</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/cVdEniplHAMcwAYRxg18gGEMQhI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Kolase-Pembakaran-Kantor-Pemerintahan-di-Papua-Tengah_1.jpg</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>IHSG Diperkirakan Kembali Menguat, Investor Wait And See Hasil Review MSCI</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:41:19 +0700</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>IHSG hari ini diperkirakan kembali menguat setelah melemah 97,49 poin pada perdagangan Selasa kemarin.</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7867186/ihsg-diperkirakan-kembali-menguat-investor-wait-and-see-hasil-review-msci</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/38xkcDnGiMqEuv_AZwgYcCu6fxg=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/dilanda-corona-ihsg-melemah_20200305_145008.jpg</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Unsur Pidana dalam Temuan 996 Senjata di Sekolah, Pengamat: Sangat Tidak Masuk Akal</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:40:15 +0700</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Temuan 996 senjata di sekolah dinilai berpotensi mengandung unsur pidana, terutama terkait izin, kepemilikan, dan penyimpanannya.</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867185/unsur-pidana-dalam-temuan-996-senjata-di-sekolah-pengamat-sangat-tidak-masuk-akal</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/tFYjnCW32FN1ESklLmCo5RFVxmM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Pengamanan-temuan-senjata-di-sekolah.jpg</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Prakiraan Cuaca Kota Surabaya, Kediri, Madiun, Blitar, Rabu 12 Agustus 2026: Cerah Berawan</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:38:37 +0700</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Simak prakiraan cuaca di Kota Surabaya, Kediri, Madiun, dan Blitar pada Rabu (12/8/2026). Seluruh wilayah tersebut diprediksi cerah berawan.</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7867184/prakiraan-cuaca-kota-surabaya-kediri-madiun-blitar-rabu-12-agustus-2026-cerah-berawan</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/d6Z05zmYE-ZlbOieHWf6t6Q66ws=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/cuaca-cerah-berawan-247.jpg</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Sejarah Hari Wanita TNI Angkatan Udara atau HUT ke-63 WARA, Diperingati 12 Agustus</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:34:08 +0700</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Hari Wanita TNI Angkatan Udara atau HUT ke-63 WARA diperingati pada 12 Agustus 2026. Sejarahnya tak lepas dari peran TNI wanita tahun 1960-an.</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867183/sejarah-hari-wanita-tni-angkatan-udara-atau-hut-ke-63-wara-diperingati-12-agustus</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/PG2vUXka7u8UBvfUMgrwHGXso1Q=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/TNl-WANlTA-345343453.jpg</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Eks Persib Kena Gocek Milik dalam Kemenangan Juventus, Pelatih Palermo: Penting Pemain Tak Cedera</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:29:31 +0700</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Mantan pemain Persib Bandung, Federico Barba, kena gocek Arkadiusz Milik saat Palermo dikalahkan Juventus 2-0 di Australia.</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7867182/eks-persib-kena-gocek-milik-dalam-kemenangan-juventus-pelatih-palermo-penting-pemain-tak-cedera</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/RvTZVRH7K9SPllyxhEm7y5TuadI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Penyerang-Persebaya-Surabaya-Bruno-Moreira-saat-dihadang-bek-Persib-Bandung-Federico-Barba.jpg</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>An Se-young Menuju Kejuaraan Dunia BWF 2026 dengan Membawa Misi Balas Dendam</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:18:06 +0700</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Misi balas dendam dibawa oleh An Se-young dalam perjalanannya menuju gelaran bergengsi Kejuaraan Dunia BWF 2026 di New Delhi.</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7867181/an-se-young-menuju-kejuaraan-dunia-bwf-2026-dengan-membawa-misi-balas-dendam</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/uhMannKbPjP6hOu9TqQPUB0D_F8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Selebrasi-An-Se-young-Final-Malaysia-Open-2026.jpg</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Komentar Ibunda Asila Maisa soal Putrinya Jadi Saksi Laporan Rizky Billar, Soroti Kebenaran</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:16:54 +0700</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Asila Maisa diperiksa sebagai saksi dalam laporan Rizky Billar soal hoaks. Sang ibunda, Avi Basalamah, ikut memberikan dukungan.</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7867180/komentar-ibunda-asila-maisa-soal-putrinya-jadi-saksi-laporan-rizky-billar-soroti-kebenaran</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/ojP31E7SsmHSHs02l0SLO4UZXrI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Asila-Maisa.jpg</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Aripat Dituding Numpang Hidup, Nathalie Holscher Bongkar Alasan Boyong Suami Tinggal di Rumahnya</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:15:11 +0700</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Arief Fadli atau akrab disapa Aripat dituding hanya numpang hidup, Nathalie Holscher membongkar alasan mengajak sang suami tinggal di rumahnya.</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7867179/aripat-dituding-numpang-hidup-nathalie-holscher-bongkar-alasan-boyong-suami-tinggal-di-rumahnya</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/K_73CdJeZNrfun2dJLzXfN_pbdc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Nathalie-Holscher-1-21102025.jpg</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Korut Tembakkan Rudal Balistik ke Timur Laut Korsel, di Luar ZEE Jepang</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:14:12 +0700</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Militer Korea Utara menembakkan setidaknya satu rudal balistik ke arah Laut Timur Korea Selatan pada Rabu pagi, 12 Agustus 2026.</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7867178/korut-tembakkan-rudal-balisti-ke-ke-timur-laut-korsel-di-luar-zee-jepang</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/R-5EYr5JxAhkh7uBXPpFZNkS-oU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Rudal-balistik-Korut-2025-OK.jpg</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Prakiraan Cuaca Bandung Raya Rabu, 12 Agustus 2026: Kota Bandung dan Cimahi Cerah</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:14:00 +0700</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Cuaca di seluruh wilayah Bandung Raya pada Rabu (12/8/2026) diprakirakan cerah, termasuk Kota Bandung dan Cimahi.</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7867177/prakiraan-cuaca-bandung-raya-rabu-12-agustus-2026-kota-bandung-dan-cimahi-cerah</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/lDgUVS5zQ1sLN8t3mHbweeriZkY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/cuaca-cerah-berawan-xx.jpg</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Jangan Pakai Nama Samaran, Ini Cara Ortu Kenalkan Organ Intim pada Anak</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:13:30 +0700</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Dokter Septian menjelaskan orang tua tidak perlu menggunakan nama samaran untuk mengenalkan organ intim kepada anak.</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/kesehatan/7867176/jangan-pakai-nama-samaran-ini-cara-ortu-kenalkan-organ-intim-pada-anak</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/5JzZqcU8Zxy0KWyxDlGXo7OMqvA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Anak-anak-SD-Kanisius-Solo.jpg</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Keluarga Sutrimo Dijaga Ketat Jelang Pembongkaran Makam di Banyumas</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:07:08 +0700</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Kuasa Hukum Aan Rohaeni ungkap keamanan dan kondisi keluarga Sutrimo jelang pembongkaran makam atau ekshumasi di Banyumas, Rabu (12/8/2026).</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867175/keluarga-sutrimo-dijaga-ketat-jelang-pembongkaran-makam-di-banyumas</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/CawjQmYsx6SChqFOdefPkSh2M4U=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Kematian-Sutrimo-Dilaporkan-ke-Polisi-oleh-Keluarga.jpg</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Dikecam Netizen usai Peluk Vokalis JET di Panggung, Aldi Taher Bersuara:Gue Peluk Bukan Colong Gitar</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:06:03 +0700</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Aldi Taher dikecam netizen usai memeluk vokalis band JET, Nic Cester, di atas panggung The Sounds Project.</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7867174/dikecam-netizen-usai-peluk-vokalis-jet-di-panggung-aldi-taher-bersuarague-peluk-bukan-colong-gitar</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/I75QaFzNwI10YfC_5Suv_vcBvaU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Aldi-taher-bisnis-ayam.jpg</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Berawal dari Penyaluran Dana Desa, 7 Kantor Pemerintah Kabupaten Puncak Papua Tengah Dibakar</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 06:50:30 +0700</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Pembakaran kantor diduga buntut dari penyaluran Dana Desa (DD) tahap pertama reguler, Selasa (11/8/2026).</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7867173/berawal-dari-penyaluran-dana-desa-7-kantor-pemerintah-kabupaten-puncak-papua-tengah-dibakar</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/tDk7IObInGCnZb1nWhJ5FdYEj4Q=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ilustrasi-kebakarannnnnnnnnnnnnnnnnnnn.jpg</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Gedung Biro Kesra di Kantor Gubernur Kalteng Kebakaran</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 06:37:03 +0700</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Berdasarkan laporan resmi dari tim kedaruratan, informasi kebakaran diterima petugas dari laporan masyarakat pada pukul 02.40 WIB.</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7867172/gedung-biro-kesra-di-kantor-gubernur-kalteng-kebakaran</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/egPXVEaAqYXtz_9JckAfbocqhvk=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Kebakaran-di-Kompleks-Kantor-Gubernur-kalteng.jpg</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Launch MotoGP 2027 Berlokasi di Rio de Janeiro, Brasil Jadi Negara Ketiga dalam 3 Tahun</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 06:33:48 +0700</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>MotoGP menunjuk Rio de Janeiro, Brasil, sebagai lokasi launch musim 2027 sekaligus melanjutkan tradisi di lokasi berbeda.</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7867171/launch-motogp-2027-berlokasi-di-rio-de-janeiro-brasil-jadi-negara-ketiga-dalam-3-tahun</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/QWRdNYbbfG5s6YXga5PrKpnEFfo=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Sprint-Race-MotoGP-Amerika-2026.jpg</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Pertanian</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Bantu Petani Lebih Efisien, 13 Sprayer Pestisida Disalurkan ke Indramayu-Majalengka</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:38:12 +0700</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Satria K Yudha</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- PT Perusahaan Perdagangan Indonesia (Persero) atau PPI menyalurkan 13 unit sprayer pestisida kepada gabungan kelompok tani (Gapoktan) di Kabupaten Indramayu dan Kabupaten Majalengka, Jawa Barat. Bantuan tersebut...</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjmsfo416/bantu-petani-lebih-efisien-13-sprayer-pestisida-disalurkan-ke-indramayumajalengka</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/penyaluran-bantuan-13-unit-sprayer-pestisida-kepada-gabungan-kelompok_260812073735-603.jpeg</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Pertanian</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Pemerintah Ancam Cabut Izin Pelaku Manipulasi Harga Pakan dan Telur</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Gita Amanda</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, SURABAYA -- Menteri Pertanian (Mentan) Andi Amran Sulaiman mengancam mencabut izin usaha pelaku manipulasi harga pakan dan telur guna menjaga stabilitas pasar dan melindungi peternak nasional.
+“Bagi siapa pun yang...</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjmrwi423/pemerintah-ancam-cabut-izin-pelaku-manipulasi-harga-pakan-dan-telur</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/menteri-pertanian-amran-sulaiman-mengunjungi-peternakan-ayam-_190130090143-326.jpg</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Kemenpar Dukung InJourney-Garuda Kasih Tiket Gratis untuk Wisman</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:00:48 +0700</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Gita Amanda</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Kementerian Pariwisata (Kemenpar) mendukung kolaborasi InJourney dan Garuda Indonesia dalam menghadirkan program Free Domestic Flight (FDF) dengan menyediakan 170.845 kursi penerbangan bagi wisatawan mancanegara (wisman) pemegang tiket...</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjmqpc423/kemenpar-dukung-injourneygaruda-kasih-tiket-gratis-untuk-wisman</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/020424200-1684842868-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Makam Sutrimo Dibongkar Hari Ini, Polisi Cari Petunjuk Kematian Tak Wajar</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:15:34 +0700</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya menggelar ekshumasi jenazah Sutrimo di Banyumas hari ini untuk mengungkap penyebab kematiannya yang dinilai tidak wajar.</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267627/makam-sutrimo-dibongkar-hari-ini-polisi-cari-petunjuk-kematian-tak-wajar</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/Ac0CwWSgaQOzoD0dmfbEg4_UyMk=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9312458/original/059177100_1785493658-IMG_1805.jpg</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Kebakaran Melanda Pabrik Bingkai di Duren Sawit</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:15:03 +0700</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Kebakaran Pabrik Bingkai melanda sebuah pabrik di Duren Sawit, Jakarta Timur, dini hari. Sekitar 100 personel damkar masih berjibaku memadamkan api.</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267632/kebakaran-melanda-pabrik-bingkai-di-duren-sawit</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/MwKrlqCPortK2p2e5h-_z2L7AFU=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321698/original/080400300_1786493694-ilustrasi_kebakaran.jpg</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Dakwaan Jaksa vs Bantahan Eks Menag Yaqut di Sidang Korupsi Kuota Haji</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:01:41 +0700</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Dalam sidang perdana, jaksa membeberkan dugaan aliran uang dan kerugian negara Rp622 miliar, sementara Yaqut membantah menerima uang dan mempertanyakan dasar dakwaan tersebut.</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267602/dakwaan-jaksa-vs-bantahan-eks-menag-yaqut-di-sidang-korupsi-kuota-haji</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/stAlPACGZORRu5DU5poKMV3z6yU=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321159/original/065738600_1786430944-ya4.jpg</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>KH Anwar Zahid Cerita Detik-Detik Mobilnya Ditabrak Truk</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 06:51:21 +0700</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>KH Anwar Zahid menceritakan kondisi dirinya setelah mobil yang ditumpanginya ditabrak truk trailer saat mengantre di lokasi perbaikan jalan.</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267625/kh-anwar-zahid-cerita-detik-detik-mobilnya-ditabrak-truk</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/cPtrbZUIV1_7u3BqpwQw6fs1kG4=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321696/original/090135600_1786492180-kh-anwar-zahid-saat-mengisi-pengajian-di-desa-sije-20260811064255.jpg</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Pemerintah Pastikan Tak Ada Peningkatan Ancaman Jelang HUT RI</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:12:46 +0700</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Pemerintah memastikan situasi keamanan nasional terkendali menjelang HUT ke-81 RI dan meminta masyarakat waspada terhadap informasi di ruang digital.</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267631/pemerintah-pastikan-tak-ada-peningkatan-ancaman-jelang-hut-ri</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/NIqGLJIZgyZbSe5Fg4VkaJUo6vs=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9316148/original/057906600_1785915445-0db335b9-1614-4759-aad0-edd8c8ddac02.jpg</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Kejari Kembali Sita Rp 1,24 Miliar dalam Kasus Korupsi Tunjangan Perumahan DPRD Ponorogo</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:59:19 +0700</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Kejari Ponorogo kembali menyita uang dalam penyidikan kasus dugaan korupsi tunjangan perumahan anggota DPRD Ponorogo</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://surabaya.kompas.com/read/2026/08/12/075757478/kejari-kembali-sita-rp-124-miliar-dalam-kasus-korupsi-tunjangan-perumahan</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/HF0Efvp2vYROPBvSi_cA43V2glE=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/12/6a7bbcce32d57.jpg</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Bola</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Jakarta Siapkan 2 Lapangan Latihan untuk Tunjang FIFA ASEAN Cup 2026</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:59:19 +0700</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Jakarta menyiapkan dua lapangan latihan untuk mendukung penyelenggaraan FIFA ASEAN Cup 2026.</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://bola.kompas.com/read/2026/08/12/07291188/jakarta-siapkan-2-lapangan-latihan-untuk-tunjang-fifa-asean-cup-2026</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/Ja9CNBTTNvY6v9XN4pb6taf8pQ8=/0x133:1600x1200/1200x675/filters:watermark(data/photo/2026/01/30/697c8163c3944.png,0,-0,1)/data/photo/2026/08/10/6a796e6e6b9f0.jpg</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Dinamika Jelang Muktamar Ke-35 NU, Muncul Usulan Ketum PBNU Ditunjuk Langsung Rais Aam</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:59:19 +0700</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Dinamika jelang Muktamar NU ke-35, usulan sistem pemilihan muncul, termasuk penguatan AHWA dan sistem voting.</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/12/07021891/dinamika-jelang-muktamar-ke-35-nu-muncul-usulan-ketum-pbnu-ditunjuk-langsung</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/baEBJu0N3bXRNX-SA8cuhT74W7c=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/06/6a73e1aa9f4de.jpg</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I81"/>
+  <autoFilter ref="A1:I133"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-12.xlsx
+++ b/data/berita_2026-08-12.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$259</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I133"/>
+  <dimension ref="A1:I259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -6685,8 +6685,5931 @@
         </is>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>74 alutsista udara termasuk Rafale tampil di Jakarta saat HUT RI</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 10:11:45 +0700</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Sebanyak 74 alat utama sistem senjata (alutsista) udara akan tampil di langit Istana Negara, Jakarta saat upacara ...</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690336/74-alutsista-udara-termasuk-rafale-tampil-di-jakarta-saat-hut-ri</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1001560157.jpg</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>DPR: Publik terbuka soal kreativitas tapi agama tak boleh dipermainkan</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 10:09:10 +0700</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Anggota Komisi VIII DPR RI Dini Rahmania menilai bahwa masyarakat sangat terbuka dengan kreativitas generasi muda ...</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690333/dpr-publik-terbuka-soal-kreativitas-tapi-agama-tak-boleh-dipermainkan</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/19/1001243379.jpg</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Petra Sihombing rilis "Bangga" ceritakan kekaguman dan kebanggaan</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 10:08:32 +0700</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Penyanyi Petra Sihombing merilis single baru berjudul "Bangga" yang menceritakan mengenai kekaguman dan ...</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690331/petra-sihombing-rilis-bangga-ceritakan-kekaguman-dan-kebanggaan</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/photo_6332406529352470841_y.jpg</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Bencic mundur dari perempat final WTA 1000 Toronto, Gauff ke semifinal</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:57:56 +0700</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Petenis Swiss Belinda Bencic mundur dari pertandingan perempat final National Bank Open 2026 di Toronto, Kanada, karena ...</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690328/bencic-mundur-dari-perempat-final-wta-1000-toronto-gauff-ke-semifinal</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/IMG_0163.jpg</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Manulife Tunjuk Jeremy Young sebagai Chief Distribution Officer, Internasional Brokerage, Global High-Net-Worth</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:55:29 +0700</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Manulife resmi menunjuk Jeremy Young sebagai Chief Distribution Officer, International Brokerage, Global ...</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690325/manulife-tunjuk-jeremy-young-sebagai-chief-distribution-officer-internasional-brokerage-global-high-net-worth</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/Jeremy-Young-Manulife.jpg</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>KuCoin Perkuat Ekosistem RWA lewat Ondo Tokenized Stocks di KuCoin Alpha</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:50:11 +0700</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>KuCoin, platform aset kripto global yang mengutamakan kepercayaan pengguna, mengintegrasikan aset tokenisasi Ondo yang ...</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690323/kucoin-perkuat-ekosistem-rwa-lewat-ondo-tokenized-stocks-di-kucoin-alpha</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/KuCoin-Ekosistem-RWA.jpg</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Polda Lampung tangkap 41 pelaku C3 dalam sehari</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:47:04 +0700</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Kepolisian Daerah (Polda) Lampung bersama jajarannya menangkap 41 pelaku kejahatan yang terdiri atas kasus pencurian ...</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690320/polda-lampung-tangkap-41-pelaku-c3-dalam-sehari</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/1001148178.jpg</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>IJBNet: SAF jadi ladang bisnis baru kemitraan Indonesia-Jepang</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:45:27 +0700</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Ketua Umum Indonesia Japan Business Network (IJBNet) Dr. Suyoto Rais mengatakan pengembangan Sustainable Aviation Fuel ...</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690319/ijbnet-saf-jadi-ladang-bisnis-baru-kemitraan-indonesia-jepang</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/1000595780.jpg</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Rupiah diprediksi konsolidatif seiring perkembangan geopolitik Timteng</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:43:42 +0700</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Nilai tukar rupiah terhadap dolar AS pada pembukaan perdagangan Rabu, bergerak melemah 8 poin atau 0,04 persen menjadi ...</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690315/rupiah-diprediksi-konsolidatif-seiring-perkembangan-geopolitik-timteng</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/09/nilai-tukar-rupiah-melemah-2819049.jpg</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Iran siapkan RUU larang kapal negara musuh masuki Teluk</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:42:38 +0700</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Parlemen Iran menyiapkan rancangan undang-undang yang melarang kapal militer dan komersial dari negara yang dianggap ...</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690311/iran-siapkan-ruu-larang-kapal-negara-musuh-masuki-teluk</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/19/Selat-Hormuz-dan-negara-Teluk.jpg</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Pandangan JustMarkets: Logam Mana yang Lebih Masuk Akal untuk Diperdagangkan Saat Ini? Perak atau Emas?</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:39:36 +0700</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>CFD emas dan perak umumnya digunakan di pasar trading, tetapi terkadang sulit untuk memilih di antara keduanya, ...</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690307/pandangan-justmarkets-logam-mana-yang-lebih-masuk-akal-untuk-diperdagangkan-saat-ini-perak-atau-emas</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/Pandangan-JustMarkets.jpg</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Ben Shelton dan Rafael Jodar melaju ke semifinal ATP Masters Montreal</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:39:11 +0700</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Petenis Amerika Serikat Ben Shelton dan petenis Spanyol Rafael Jodar melaju ke semifinal National Bank Open 2026 di ...</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690303/ben-shelton-dan-rafael-jodar-melaju-ke-semifinal-atp-masters-montreal</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/IMG_0162.jpeg</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>MTI: Alih kelola transportasi Kepulauan Seribu butuh kesiapan sistem</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:38:54 +0700</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Dewan Penasehat Masyarakat Transportasi Indonesia (MTI) Djoko Setijowarno mengatakan pengalihan pengelolaan ...</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690299/mti-alih-kelola-transportasi-kepulauan-seribu-butuh-kesiapan-sistem</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/20260811105212.jpeg</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Sentuhan Xi Jinping dalam Diplomasi China</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:37:49 +0700</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>"Persahabatan dijalin berlandaskan hal yang bermakna, yakni dunia yang damai haruslah dunia yang penuh ...</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690295/sentuhan-xi-jinping-dalam-diplomasi-china</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/CjkinzN000002_20260812_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Harga emas Antam pada Rabu ini anjlok Rp30.000 jadi Rp2,680 juta/gr</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:36:37 +0700</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Harga emas Antam yang dipantau dari laman Logam Mulia, di Jakarta, Rabu pukul 9.29 WIB turun Rp30.000 ke angka ...</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690293/harga-emas-antam-pada-rabu-ini-anjlok-rp30000-jadi-rp2680-juta-gr</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/04/1000192312.jpg</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>BPBD: Tujuh warga meninggal dunia tertimpa pohon di Pidie</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:33:44 +0700</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Badan Penanggulangan Bencana Daerah (BPBD) Kabupaten Pidie, Provinsi Aceh, menyatakan sebanyak tujuh warga meninggal ...</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690292/bpbd-tujuh-warga-meninggal-dunia-tertimpa-pohon-di-pidie</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/pohon-tumbang-pidie_1.jpeg</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Hakim AS blokir aturan Trump soal pemungutan suara lewat pos</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:32:32 +0700</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Seorang hakim federal pada Selasa memblokir layanan pos Amerika Serikat (USPS) yang menerapkan ketentuan perintah ...</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690288/hakim-as-blokir-aturan-trump-soal-pemungutan-suara-lewat-pos</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/thumbs_b_c_ab5d296d556bf61eed768b8ca4900658.jpg</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>IHSG menguat di tengah "wait and see" tinjauan MSCI periode Agustus</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:32:24 +0700</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Rabu bergerak menguat di tengah pelaku pasar ...</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690285/ihsg-menguat-di-tengah-wait-and-see-tinjauan-msci-periode-agustus</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IHSG-ditutup-menguat-65-94-poin-070826-Fah-2.jpg</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Supermodel Alessandra Ambrosio bertunangan dengan Buck Palmer</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:26:57 +0700</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Model Victoria Secret, Alessandra Ambrosio bertunangan dengan kekasihnya yakni Buck Palmer pada Selasa ...</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690284/supermodel-alessandra-ambrosio-bertunangan-dengan-buck-palmer</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/photo_6332406529352470830_w.jpg</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Akademisi sebut pentingnya bangun rantai nilai terintegrasi hilirisasi</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:26:12 +0700</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Guru Besar Fakultas Teknik Universitas Andalas (Unand) Is Prima Nanda mengungkapkan pentingnya kemampuan membangun ...</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690280/akademisi-sebut-pentingnya-bangun-rantai-nilai-terintegrasi-hilirisasi</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/1044.jpg</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Dispar Kaltim kibarkan bendera di bawah laut bersama hiu pada HUT RI</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:26:00 +0700</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Dinas Pariwisata Kalimantan Timur menjadwalkan aksi spektakuler pengibaran Bendera Merah Putih di bawah laut bersama ...</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690276/dispar-kaltim-kibarkan-bendera-di-bawah-laut-bersama-hiu-pada-hut-ri</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/IMG_3822.jpeg</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Tim SAR evakuasi penumpang KMP Putri Yasmin terbakar di Selat Lombok</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:24:52 +0700</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Kantor SAR Mataram bersama tim gabungan saat ini tengah melakukan operasi SAR intensif menyusul insiden kebakaran yang ...</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690275/tim-sar-evakuasi-penumpang-kmp-putri-yasmin-terbakar-di-selat-lombok</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/1001805223.jpg</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya pastikan ekshumasi Sutrimo sesuai jadwal</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:19:35 +0700</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya memastikan ekshumasi atau pembongkaran makam terhadap jenazah Sutrimo di Banyumas, Jawa Tengah, ...</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690271/polda-metro-jaya-pastikan-ekshumasi-sutrimo-sesuai-jadwal</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/IMG_20260327_114917.jpg</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Kebakaran melanda pabrik bingkai di Duren Sawit Jaktim</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:12:33 +0700</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Kebakaran melanda sebuah pabrik bingkai di Jalan Lampiri, RT 04/RW 12, Kelurahan Pondok Kelapa, Duren Sawit, Jakarta ...</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690269/kebakaran-melanda-pabrik-bingkai-di-duren-sawit-jaktim</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/InShot_20260812_083445716.jpg</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Rupiah pada Rabu pagi melemah jadi Rp17.869 per dolar AS</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:08:15 +0700</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Nilai tukar rupiah terhadap dolar Amerika Serikat (AS) pada pembukaan perdagangan Rabu, bergerak melemah 8 poin atau ...</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690265/rupiah-pada-rabu-pagi-melemah-jadi-rp17869-per-dolar-as</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/07/23/antarafoto-rupiah-ditutup-melemah-030924-adm-3.jpg</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Kader dan Posyandu Duri Pulo wakili Jakpus di tingkat Provinsi</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:06:34 +0700</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Kader dan Posyandu Melati 2 Duri Pulo mewakili Jakarta Pusat (Jakpus) dalam Penilaian Bidang Kesehatan Tingkat ...</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690263/kader-dan-posyandu-duri-pulo-wakili-jakpus-di-tingkat-provinsi</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/1000836715.jpg</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Harimau sumatra masuk kandang jebak BKSDA Sumbar usai makan ternak</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:05:33 +0700</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Satu individu harimau sumatra masuk kandang jebak milik Balai Konservasi Sumber Daya Alam (BKSDA) Sumatera Barat di ...</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690259/harimau-sumatra-masuk-kandang-jebak-bksda-sumbar-usai-makan-ternak</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/1001148395.jpg</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Komisi III DPR uji kelayakan calon Hakim Agung hari ini</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:05:29 +0700</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Komisi III DPR RI akan menggelar uji kelayakan dan kepatutan atau fit and proper test terhadap calon Hakim Agung, calon ...</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690255/komisi-iii-dpr-uji-kelayakan-calon-hakim-agung-hari-ini</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/01/26/Uji-kelayakan-dan-kepatutan-Hakim-MK-260126-Ada-6.jpg</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>IHSG Rabu dibuka menguat 9,88 poin ke posisi 6.277</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:05:02 +0700</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Rabu pagi dibuka menguat 9,88 poin atau 0,16 persen ...</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690253/ihsg-rabu-dibuka-menguat-988-poin-ke-posisi-6277</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IHSG-ditutup-menguat-65-94-poin-070826-Fah-1.jpg</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Hari Gajah 2026: Jaga eksistensi gajah nusantara</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:00:53 +0700</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Sebutan “anak online” atau “anak daring” biasanya disematkan kepada bayi-bayi manusia yang ...</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690251/hari-gajah-2026-jaga-eksistensi-gajah-nusantara</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/WhatsApp-Image-2026-08-12-at-08.05.48.jpeg</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Langkah meningkatkan kepatuhan angkutan barang</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Lebih dari 70 persen kendaraan angkutan barang tercatat mematuhi aturan dimensi dan muatan pada 2026. Kementerian ...</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/infografik/5690152/langkah-meningkatkan-kepatuhan-angkutan-barang</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/20260812-Meningkatkan-angkutan-barang-patuh-aturan_3.jpg</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Warga Gandaria Utara berlomba wujudkan ketahanan pangan sambut HUT RI</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:59:21 +0700</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Warga RT 11/RW 07, Kelurahan Gandaria Utara, Jakarta Selatan, berlomba mewujudkan ketahanan pangan dalam rangka ...</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690249/warga-gandaria-utara-berlomba-wujudkan-ketahanan-pangan-sambut-hut-ri</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/1001024170.jpg</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Kementerian PU optimalkan Bendungan Tapin Kalsel jaga ketersediaan air</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:58:11 +0700</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Kementerian Pekerjaan Umum (PU) mengoptimalkan peran Bendungan Tapin di Kecamatan Piani Kabupaten Tapin, Kalimantan ...</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690245/kementerian-pu-optimalkan-bendungan-tapin-kalsel-jaga-ketersediaan-air</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/1043.jpg</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>BKPM sebut NIB permudah akses pembinaan dan pembiayaan UMKM</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:53:22 +0700</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Kementerian Investasi dan Hilirisasi/Badan Koordinasi Penanaman Modal (BKPM) menyampaikan pentingnya kepemilikan Nomor ...</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690243/bkpm-sebut-nib-permudah-akses-pembinaan-dan-pembiayaan-umkm</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/DDK07050_edit_403990302636269.jpg</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>MK gelar sidang pengucapan putusan 15 permohonan uji materiil hari ini</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:50:21 +0700</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Mahkamah Konstitusi (MK) dijadwalkan menggelar sidang pengucapan putusan atau ketetapan atas 15 permohonan uji materiil ...</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690239/mk-gelar-sidang-pengucapan-putusan-15-permohonan-uji-materiil-hari-ini</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/24/1000001944.jpg</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Mendag dorong industri otomotif maksimalkan perjanjian dagang</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:50:05 +0700</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Menteri Perdagangan (Mendag) Budi Santoso mendorong pelaku usaha di sektor otomotif untuk terus meningkatkan ekspor dan ...</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690237/mendag-dorong-industri-otomotif-maksimalkan-perjanjian-dagang</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/IMG_3754.jpeg</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Trump sebut punya tiga strategi hadapi Iran, termasuk eskalasi</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:43:53 +0700</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Presiden Amerika Serikat Donald Trump pada Selasa (11/8) mengatakan negaranya memiliki tiga cara untuk menghadapi Iran, ...</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690236/trump-sebut-punya-tiga-strategi-hadapi-iran-termasuk-eskalasi</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/thumbs_b_c_2263c951fe4876ab38332a738c829d57-1.jpg</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Presiden Lebanon: Israel harus tinggalkan wilayah kami</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:34:11 +0700</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Lebanon tidak akan membiarkan Israel untuk terus berada di wilayahnya dan akan mengupayakan penarikan penuh pasukan ...</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690233/presiden-lebanon-israel-harus-tinggalkan-wilayah-kami</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/25/Joseph-Aoun-Presiden-Lebanon.jpg</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>PIHPS: Harga cabai rawit Rp61.350/kg, telur ayam Rp29.450/kg</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:28:23 +0700</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Pusat Informasi Harga Pangan Strategis (PIHPS) Nasional yang dikelola Bank Indonesia, mencatat harga komoditas cabai ...</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690229/pihps-harga-cabai-rawit-rp61350-kg-telur-ayam-rp29450-kg</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/22FB56E5-0EFD-48F4-B5F6-09ED50B2D6CF.jpeg</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>PII komit tingkatkan pelayanan sertifikasi insinyur</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:23:31 +0700</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Persatuan Insinyur Indonesia (PII) menyatakan berkomitmen meningkatkan pelayanan sertifikasi insinyur untuk mempercepat ...</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690227/pii-komit-tingkatkan-pelayanan-sertifikasi-insinyur</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/WhatsApp-Image-2026-08-11-at-17.01.12.jpg</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Wanita korban gempa Kolombia selamat usai 30 jam terjebak reruntuhan</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:14:23 +0700</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Tim penyelamat di Kota Cali, Kolombia berhasil mengevakuasi seorang wanita bernama Diana yang terjebak selama sekitar ...</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690224/wanita-korban-gempa-kolombia-selamat-usai-30-jam-terjebak-reruntuhan</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/gempa1.jpg</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Megawati harap Bamusi jadi ormas perekat umat</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:07:14 +0700</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Ketua Umum PDI Perjuangan Megawati Soekarnoputri berharap organisasi sayap PDIP, Baitul Muslimin Indonesia (Bamusi), ...</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690221/megawati-harap-bamusi-jadi-ormas-perekat-umat</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/12/1000482159.jpg</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Kemarin, usul insentif ibu rumah tangga hingga tak ada PPPK dirumahkan</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:57:08 +0700</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Berbagai peristiwa politik kemarin yang menjadi sorotan, di antaranya Anggota DPR RI Viktor Laiskodat mengusulkan ...</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690217/kemarin-usul-insentif-ibu-rumah-tangga-hingga-tak-ada-pppk-dirumahkan</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/raker-komisi-ii-dpr-dengan-kemendagri.jpg</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Rabu, gerai Samsat Keliling tersedia di 14 wilayah Jadetabek</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:53:34 +0700</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya menyediakan layanan Sistem Administrasi Manunggal Satu Atap (Samsat) Keliling di 14 wilayah yang ...</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690213/rabu-gerai-samsat-keliling-tersedia-di-14-wilayah-jadetabek</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/09/1000841589.jpg</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Layanan SIM Keliling tersedia di lima lokasi Jakarta pada Rabu</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:47:10 +0700</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Direktorat Lalu Lintas (Ditlantas) Polda Metro Jaya membuka layanan Surat Izin Mengemudi (SIM) Keliling di lima lokasi ...</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690207/layanan-sim-keliling-tersedia-di-lima-lokasi-jakarta-pada-rabu</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/04/21/IMG_20241216_173711.jpg.jpg</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Kemarin, Yaqut siapkan 1 juta dolar hingga KPK singgung Ridwan Kamil</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:45:11 +0700</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Berbagai peristiwa hukum kemarin yang menjadi sorotan, di antaranya mantan Menteri Agama Yaqut Cholil Qoumas didakwa ...</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690205/kemarin-yaqut-siapkan-1-juta-dolar-hingga-kpk-singgung-ridwan-kamil</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/11/Yaqut-Cholil-Didakwa-Rugikan-Negara-Ratusan-Miliar-110826-Bay-2.jpg</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>20 personel padamkan kebakaran rumah di Kramat Jati Jaktim</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:41:31 +0700</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Sebanyak 20 personel Suku Dinas Penanggulangan Kebakaran dan Penyelamatan (Sudin Gulkarmat) Jakarta Timur (Jaktim) ...</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5690201/20-personel-padamkan-kebakaran-rumah-di-kramat-jati-jaktim</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/09/20/InShot_20250920_120935722.jpg</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Andre Rosiade Siap Fasilitasi Penyelesaian Aduan Konsumen Perumahan Adhi Commuter Properti</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 10:12:56 +0700</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Tim detikcom</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Komisi VI DPR RI terima audiensi konsumen PT Adhi Commuter Properti Tbk. Mereka bahas masalah proyek hunian yang belum selesai dan cari solusi konkret.</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614787/andre-rosiade-siap-fasilitasi-penyelesaian-aduan-konsumen-perumahan-adhi-commuter-properti</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/12/andre-rosiade-menerima-aduan-dari-konsumen-perumahan-pt-adhi-commuter-properti-tbk-9dok-istimewa-1786504199678_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Menkes Ingatkan Siswa Sekolah Rakyat Jaga Kesehatan: Sikat Gigi yang Benar</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:56:18 +0700</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Hana Nushratu</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Menkes Budi Gunadi Sadikin mengingatkan siswa Sekolah Rakyat untuk menjaga kesehatan gigi, pola makan, dan rutin berolahraga demi kesehatan optimal.</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614759/menkes-ingatkan-siswa-sekolah-rakyat-jaga-kesehatan-sikat-gigi-yang-benar</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/12/menkes-ingatkan-siswa-sekolah-rakyat-jaga-kesehatan-rajin-sikat-gigi-1786503316643.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Sidang Perdana 11 Tersangka Korupsi Limbah Sawit Rp 7,3 T Digelar 18 Agustus</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:56:04 +0700</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Mulia Budi</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Sidang perdana 11 tersangka korupsi ekspor limbah sawit digelar pekan depan. Kerugian negara diperkirakan mencapai Rp 7,3 triliun.</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614758/sidang-perdana-11-tersangka-korupsi-limbah-sawit-rp-7-3-t-digelar-18-agustus</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/02/12/ilustrasi-sidang-vonis_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>KMP Putri Yasmin Terbakar di Pantai Sekotong Lombok Barat, Tim SAR Dikerahkan</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:38:31 +0700</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Ahmad Viqi, Sui Suadnyana</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>KMP Putri Yasmin terbakar di Pantai Sekotong, Lombok. Penumpang panik, tim SAR dikerahkan untuk evakuasi.</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614737/kmp-putri-yasmin-terbakar-di-pantai-sekotong-lombok-barat-tim-sar-dikerahkan</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/12/kmp-putri-yasmin-dok-maritimeoptimacom-1786498532198_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Polda Riau Tetapkan 2 Tersangka Kasus Karhutla di Area HGU Bengkalis</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:34:43 +0700</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Mei Amelia R</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Polda Riau ungkap kasus kebakaran hutan di PT TKWL, menetapkan dua tersangka. Penyidikan mendalam dilakukan untuk mengungkap penyebab dan dampak ekologisnya.</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614735/polda-riau-tetapkan-2-tersangka-kasus-karhutla-di-area-hgu-bengkalis</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/12/karhutla-di-areal-hgu-di-bengkalis-1786502063551_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Ekshumasi Jenazah Sutrimo Digelar Pagi Ini, Dipimpin Brigjen Hastry</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:12:33 +0700</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya melakukan ekshumasi jenazah Sutrimo di TPU Banyumas untuk penyelidikan lebih lanjut. Keluarga memilih tidak hadir dalam proses tersebut.</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614715/ekshumasi-jenazah-sutrimo-digelar-pagi-ini-dipimpin-brigjen-hastry</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/kabid-humas-polda-metro-jaya-kombes-budi-hermanto-1786089469736_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Disbudpar Cabut Status Runner Up Raka Jatim 2026 yang Minta Pacar Aborsi</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:01:41 +0700</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Faiq Azmi</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Disbudpar Jatim cabut status Tio Ferdian Rahmana sebagai Wakil I Raka Jatim 2026 akibat pelanggaran kode etik. Atribut dan hadiah harus dikembalikan.</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614703/disbudpar-cabut-status-runner-up-raka-jatim-2026-yang-minta-pacar-aborsi</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/09/runner-up-raka-raki-jawa-timur-2026-diduga-minta-pacar-aborsi-ke-singapura-1786280246592_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Rekayasa Wanita Bunuh Diri di Tangerang Ternyata Dibunuh Pacar Sendiri</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:54:41 +0700</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Arief Ikhsanudin</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Seorang perempuan ditemukan tewas tergantung di kontrakan kawasan Kabupaten Tangerang. Bukan bunuh diri, wanita itu ternyata dibunuh pacar sendiri.</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614680/rekayasa-wanita-bunuh-diri-di-tangerang-ternyata-dibunuh-pacar-sendiri</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/seorang-perempuan-ditemukan-tewas-tergantung-di-kontrakan-kawasan-kabupaten-tangerang-bukan-bunuh-diri-wanita-itu-ternyata-dib-1786451751229_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Polresta Sidoarjo Raih Juara Ketahanan Pangan dan Tata Kelola SPPG</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:50:28 +0700</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Mei Amelia R</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Polresta Sidoarjo raih dua penghargaan di Malam Apresiasi Kreasi Polri. Penghargaan ini sebagai motivasi untuk terus berinovasi dan melayani masyarakat.</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614675/polresta-sidoarjo-raih-juara-ketahanan-pangan-dan-tata-kelola-sppg</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/12/polresta-sidoarjo-meraih-dua-penghargaan-di-malam-apresiasi-kreasi-polri-untuk-masyarakat-1786499306554_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Jenazah Sutrimo Bakal Diekshumasi Hari Ini, Keluarga: Ikhlas Apa Pun Hasilnya</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:44:02 +0700</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Anang Firmansyah</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Keluarga Sutrimo bersiap untuk ekshumasi jenazah hari ini di Banyumas. Meski diliputi kesedihan, mereka ikhlas menerima hasilnya.</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614673/jenazah-sutrimo-bakal-diekshumasi-hari-ini-keluarga-ikhlas-apa-pun-hasilnya</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/sutrimo-1786456968849_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>4 Fakta Rampok Pegawai Koperasi Gondol Duit Puluhan Juta di Bekasi</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:31:28 +0700</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Tim detikcom</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Uang pegawai koperasi di Cibitung dirampok komplotan bersenjata tajam. Pelaku telah ditangkap, diketahui telah beraksi tiga kali di Bekasi dan Jakarta Timur.</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614663/4-fakta-rampok-pegawai-koperasi-gondol-duit-puluhan-juta-di-bekasi</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/09/perampokan-nasabah-bank-di-siang-bolong-di-cibitung-bekasi-1786238003822_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Info Kemacetan di Tol Jakarta Rabu Pagi: Dalkot dan Jagorawi Padat</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:23:21 +0700</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Isal Mawardi</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Kepadatan lalu lintas terjadi di tol Jakarta pagi ini. Jasa Marga melaporkan beberapa titik macet akibat peningkatan volume lalin.</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614661/info-kemacetan-di-tol-jakarta-rabu-pagi-dalkot-dan-jagorawi-padat</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/07/10/penampakan-macet-panjang-di-tol-dalam-kota-cawang-arah-kuningan-2_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Transportasi Kep Seribu Akan Dialihkan ke TransJ, Kapal Tradisional Dirangkul</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:13:51 +0700</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Kadek Melda Luxiana</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Pemprov DKI Jakarta berkomitmen meningkatkan layanan transportasi publik di Kepulauan Seribu dengan melibatkan Transjakarta dan kapal tradisional.</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614647/transportasi-kep-seribu-akan-dialihkan-ke-transj-kapal-tradisional-dirangkul</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/09/23/kepala-dinas-dukcapil-dki-jakarta-budi-awaluddin_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Polisi Selidiki dugaan Penistaan Agama soal Challenge Hafalan Qur'an di Festival Musik</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:58:00 +0700</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Trypama Randra</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Promosi minuman keras berkedok tantangan (challenge) hafalan Al-Qur'an saat konser musik The Sounds Project di Ancol, Jakarta Utara (Jakut), berbuntut panjang.</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614418/polisi-selidiki-dugaan-penistaan-agama-soal-challenge-hafalan-quran-di-festival-musik</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/11/detik-pagi-polisi-selidiki-dugaan-penistaan-agama-soal-challenge-hafalan-quran-di-festival-musik-1786462041362_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>5 Hal Diungkap saat Saepul Reka Ulang Mutilasi Pria di Depok</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:47:49 +0700</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Reka ulang kasus mutilasi pria K di Depok melibatkan tersangka Saepul yang memperagakan 51 adegan. Polisi ungkap fakta baru dan kesaksian saksi mahkota.</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614612/5-hal-diungkap-saat-saepul-reka-ulang-mutilasi-pria-di-depok</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/12/rekonstruksi-kasus-mutiliasi-pria-di-depok-tersangka-saepul-dihadirkan-1786495419999_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Polres Bogor Juara 2 Inovasi Ketahanan Pangan, Raih Penghargaan dari Kapolri</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:40:59 +0700</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Tim detikcom</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Polres Bogor meraih Juara 2 Inovasi Tingkat Polres Kluster I dalam Apresiasi Kreasi Polri. Penghargaan ini mencerminkan sinergi antara kepolisian dan masyarakat</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8614609/polres-bogor-juara-2-inovasi-ketahanan-pangan-raih-penghargaan-dari-kapolri</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/12/polres-bogor-meraih-juara-2-inovasi-tingkat-polres-kluster-i-dalam-ajang-apresiasi-kreasi-polri-untuk-masyarakat-1786495098611_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>LPG 3 Kg Bakal Diganti, CNG 3 Kg Diuji Coba Pekan Depan</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:34:56 +0700</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Menteri ESDM Bahlil Lahadalia umumkan uji coba tabung CNG 3 kg sebagai pengganti LPG 3 kg. Uji coba akan dilakukan pekan depan di kota-kota besar.</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8614736/lpg-3-kg-bakal-diganti-cng-3-kg-diuji-coba-pekan-depan</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/12/14/cng-gaslink-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Harga Emas Antam Ambruk!</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:30:09 +0700</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Harga emas Antam hari ini turun Rp 30.000 per gram menjadi Rp 2.680.000. Rincian harga untuk berbagai ukuran juga disertakan.</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8614728/harga-emas-antam-ambruk</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/01/12/antam-hadirkan-emas-batangan-edisi-imlek-ini-penampakannya_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Dolar AS Pagi Ini Menguat ke Rp 17.868</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:26:10 +0700</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Nilai tukar dolar AS menguat terhadap Rupiah di level Rp 17.868. Pergerakan mata uang lainnya cenderung stagnan.</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8614725/dolar-as-pagi-ini-menguat-ke-rp-17-868</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/10/rupiah-masih-tertekan-dolar-as-betah-di-level-rp18000-1783662450657_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>IHSG Hari Ini Dibuka Menguat ke 6.277</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:19:39 +0700</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Herdi Alif Al Hikam</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) pagi ini dibuka di zona hijau. IHSG naik mendekati level 6.300.</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8614720/ihsg-hari-ini-dibuka-menguat-ke-6-277</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/11/19/ihsg-ditutup-menguat-3_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>IHSG Tergelincir ke Zona Merah, Simak Rekomendasi Saham Hari Ini</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:39:27 +0700</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Redaksi Detik</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>IHSG turun 1,53% di tengah penantian MSCI Review. GULA ekspansi bisnis, ITMG catat laba US$109,5 juta, dan LABS siapkan buyback.</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8614668/ihsg-tergelincir-ke-zona-merah-simak-rekomendasi-saham-hari-ini</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/12/bursa-dan-valas-1786498068-1786498069259.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Akta Kelahiran Langsung Terbit Usai Bayi Lahir, Begini Penjelasannya</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:30:56 +0700</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Herdi Alif Al Hikam</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Akta kelahiran dapat diterbitkan secara otomatis dan dikirim secara daring sesaat setelah bayi lahir di fasilitas kesehatan.</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8614639/akta-kelahiran-langsung-terbit-usai-bayi-lahir-begini-penjelasannya</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/07/14/cetak-akta-kelahiran-online-cara-mudah-dan-terbaru-2022_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Iran-AS Masih Ribut soal Selat Hormuz, Harga Minyak Naik Lagi</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:00:10 +0700</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Herdi Alif Al Hikam</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Harga minyak mentah Brent, patokan internasional, naik 1,36% dan ditutup pada US$ 88,91 per barel.</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8614597/iran-as-masih-ribut-soal-selat-hormuz-harga-minyak-naik-lagi</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/13/perundingan-damai-gagal-trump-perintahkan-blokade-selat-hormuz-1776052199145_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Arafah dan Halda Ditawarkan Umrah oleh Raffi Ahmad: Kayak Ajak ke Bandung</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 10:05:33 +0700</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Arafah dan Halda Rianta menerima ajakan Raffi Ahmad untuk umrah bareng. Ini perasaan Halda dan Arafah tiba-tiba diajak umrah Raffi.</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8614726/arafah-dan-halda-ditawarkan-umrah-oleh-raffi-ahmad-kayak-ajak-ke-bandung</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/12/arafah-dan-halda-1786501628589_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Cie... Jonathan Frizzy Puji Ririn Dwi Arianti</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:09:30 +0700</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Jonathan Frizzy dan Ririn Dwi Arianti siap melangkah ke pernikahan tahun depan. Ijonk mengungkapkan Ririn sebagai soulmate dan minta doa untuk kelancaran.</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8612527/cie-jonathan-frizzy-puji-ririn-dwi-arianti</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/06/15/jonathan-frizzy-dan-ririn-dwi-ariyanti-6_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Penyanyi India Sukriti Kakar Dilamar Pengusaha Shoumik Shetty di Tengah Jalan</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:26:55 +0700</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Ada kabar bahagia dari penyanyi India Sukriti Kakar. Ia habis dilamar kekasih.</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8614649/penyanyi-india-sukriti-kakar-dilamar-pengusaha-shoumik-shetty-di-tengah-jalan</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/12/sukriti-kakar-1786497349764_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Iis Dahlia soal Hubungan Baila no na dengan Devano</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:12:13 +0700</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>wes</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Iis Dahlia turut ditanya soal hubungan putranya, Devano, dengan Baila member no na.</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8612449/iis-dahlia-soal-hubungan-baila-no-na-dengan-devano</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/01/devano-danendra-1764569029119_169.webp?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy S26 FE Segera Hadir, Harganya Tembus Rp16 Juta</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 10:16:24 +0700</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Spek Samsung Galaxy S26 FE disebut tak berbeda jauh dari Galaxy S25 FE. Selain itu, harganya diprediksi melambung hingga Rp16 juta.</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/techno/7867262/samsung-galaxy-s26-fe-segera-hadir-harganya-tembus-rp16-juta</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/wdm1BBd1uQoBjSzWKpsiGZu1EVg=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/SAMSUNG-GALAXY-S25-FE-346534653465.jpg</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Sektor Penyelamat Indonesia di Tiga Edisi Kejuaraan Dunia BWF, Ganda Putra Kembali Dinanti</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 10:14:57 +0700</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Sektor ganda putra, ganda putri, dan tunggal putri menyelamatkan Merah-Putih dari paceklik podium di 3 edisi terakhir Kejuaraan Dunia BWF.</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7867261/sektor-penyelamat-indonesia-di-tiga-edisi-kejuaraan-dunia-bwf-ganda-putra-kembali-dinanti</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/9DUEarw3fEikQyPFZ2QlqI8393w=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/indonesia-open-2023-apriyanifadia-lolos-ke-babak-16-besar_20230614_191258.jpg</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Kasus Korupsi Ekspor CPO Rugikan Negara Rp 7,3 Triliun, 11 Terdakwa Disidang Selasa Pekan Depan</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 10:14:49 +0700</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>PN Jakarta Pusat telah menjadwalkan sidang dugaan korupsi ekspor CPO yang merugikan negara hingga Rp7,3 triliun pada Selasa pekan depan.</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867260/kasus-korupsi-ekspor-cpo-rugikan-negara-rp-73-triliun-11-terdakwa-disidang-selasa-pekan-depan</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/MGXIg3seyuJezLtZvV__GuVgQ9c=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/tersangka-korupsi-ekspor-CPO-3201.jpg</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Bisa Olah 500 Kg Sampah Organik Per Hari, Dua Biodigester Dibangun di Rusunawa Rorotan</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 10:12:55 +0700</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Bank Jakarta membangun 2 biodigester komunal di Jakarta Utara yang bisa mengolah 500 kg sampah organik per hari menjadi biogas dan pupuk organik.</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7867259/bisa-olah-500-kg-sampah-organik-per-hari-dua-biodigester-dibangun-di-rusunawa-rorotan</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/rXXHUjHSKo2iR6RHx5V7-Ctcc0I=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Biodigester-di-Rusunawa-Rorotan-OK.jpg</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Sosok Mahasiswa yang Tewaskan Polisi di Bandung, Pinjam Mobil TNI, Akui Tak Merasa Menabrak</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 10:11:46 +0700</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>A, mahasiswa yang mabuk di Kota Bandung, menabrak polisi hingga tewas. Namun, ia mengaku tidak merasa telah menabrak orang.</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7867258/sosok-mahasiswa-yang-tewaskan-polisi-di-bandung-pinjam-mobil-tni-akui-tak-merasa-menabrak</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/oDHF3QgbXBkk4TV6G5YdbGqHkVY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/mahasiswa-mabuk-tabrak-polisi-di-Bandung.jpg</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Prakiraan Cuaca Papua Besok Kamis, 13 Agustus 2026: Kota Jayapura Berawan, Biak Numfor Hujan</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 10:11:39 +0700</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Simak selengkapnya prakiraan cuaca di wilayah Papua Kamis, 13 Agustus 2026. Kota Jayapura berawan.</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7867257/prakiraan-cuaca-papua-besok-kamis-13-agustus-2026-kota-jayapura-berawan-biak-numfor-hujan</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/C0Jf0IytvmvYsBCV4sKCeJBN_3g=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Cuaca-berawan-hari-ini.jpg</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>MUI Cari Penggagas Gimik Promosi Miras dengan Ayat Alquran, Minta Penyelenggara Tak Lepas Tangan</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 10:08:10 +0700</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>MUI meminta seluruh pihak membuka informasi secara jelas agar persoalan tersebut dapat ditelusuri secara objektif.</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7867256/mui-cari-penggagas-gimik-promosi-miras-dengan-ayat-alquran-minta-penyelenggara-tak-lepas-tangan</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/VbLzgKc8rOQTHIZ1R3u9a2bRk48=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Wawancara-Kiai-Cholil-Nafis_20260216_212623.jpg</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>KMP Putri Yasmin Rute Padangbai-Lembar Terbakar di Selat Lombok, Penumpang Dievakuasi</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 10:08:01 +0700</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>KMP Putri Yasmin terbakar di Selat Lombok, penumpang dievakuasi tim SAR gabungan dengan bantuan kapal sekitar.</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7867255/kmp-putri-yasmin-rute-padangbai-lembar-terbakar-di-selat-lombok-penumpang-dievakuasi</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/mDl-p4qXzR8g3_OaV2zyevHHdLY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/KMP-Putri-Yasmin-rute-PadangbaiLembar-terbakar-di-Selat-Lombok-Rabu-1282026.jpg</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Komisi III DPR Desak Kematian Winda Lorenza Diusut Transparan, Ditemukan Senjata Api Milik Polisi</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 10:05:03 +0700</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Komisi III DPR RI mendesak pengusutan transparan atas kematian janggal Winda Lorenza Gowasa yang diduga tewas ditembak di rumah mantan suaminya.</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7867254/komisi-iii-dpr-desak-kematian-winda-lorenza-diusut-transparan-ditemukan-senjata-api-milik-polisi</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/IvLG4pQv_iMIgU2ahNelJsBPayU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/RDP-TERTUTUP-MANTAN-istri-polisi-di-medan.jpg</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Update Ruben Onsu Kini Pasrah soal Hak Asuh, Sarwendah Belum Ada Aksi Temukan Anak dan Ayah</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 10:04:02 +0700</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Nanda Persada sebut Sarwendah belum ada aksi pertemukan Ruben Onsu dan anak-anaknya</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7867253/update-ruben-onsu-kini-pasrah-soal-hak-asuh-sarwendah-belum-ada-aksi-temukan-anak-dan-ayah</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/vxemmMAeJ6xXTgYKO3tDO16iMwc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Ruben-Onsu-2-31072025.jpg</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Buntut Syuting Tanpa Naskah, Aktor Razan Zu Akui Gugup Main Film Dan Bandung</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 10:02:34 +0700</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Razan Zu sempat gugup saat syuting Dan Bandung. Ia harus beradaptasi dengan metode produksi tanpa skrip atau skrip dan banyak improvisasi.</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7867252/buntut-syuting-tanpa-naskah-aktor-razan-zu-akui-gugup-main-film-dan-bandung</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/6EDDTvunQfBC0soRmze8bTz905g=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Razan-Zu-1-27082025.jpg</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Alasan Keluarga Sutrimo Tak Hadiri Ekshumasi, Ibu Almarhum Masih Syok, Kuasa Hukum: Bukan Hal Mudah</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 10:01:20 +0700</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Keluarga Sutrimo memutuskan tak hadir proses ekshumasi, Rabu (12/8/2026), dengan alasan menjaga psikologis sang ibu.</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867251/alasan-keluarga-sutrimo-tak-hadiri-ekshumasi-ibu-almarhum-masih-syok-kuasa-hukum-bukan-hal-mudah</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/f7DyO2EmnkcQ3WXGKuxUk6js6Yo=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/EKSHUMASI-MAKAM-Suasana-makam-Sutrimo.jpg</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Eks Manajer Sayangkan Video CCTV Pertengkaran Ruben Onsu-Sarwendah Dibongkar ke Publik, Singgung Ego</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 10:00:31 +0700</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Eks manajer Sarwendah, Nanda Persada menyayangkan aksi saling bongkar aib antara Ruben Onsu dan mantan istri. Singgung soal ego.</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7867250/eks-manajer-sayangkan-video-cctv-pertengkaran-ruben-onsu-sarwendah-dibongkar-ke-publik-singgung-ego</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/lvuIjE6dzlQJwtBvjPB7zKFjq8A=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Ruben-Onsu-bertemu-anak1.jpg</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Terungkap Awal Perkenalan Bedu dengan Pacar Baru, Bermula dari DM Instagram</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:58:30 +0700</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Awal perkenalan komedian Bedu dengan kekasih barunya, Fatieh Aton terungkap, bermula dari direct message (DM) Instagram.</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7867249/terungkap-awal-perkenalan-bedu-dengan-pacar-baru-bermula-dari-dm-instagram</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/P0pzCLuXcCVY3ay30iZIbwLwdUA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Bedu-batasi-kolom-komentar-Instagram-usai-gugat-cerai-istrinya.jpg</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Menikah dengan WNI, WN Myanmar Diduga Tinggal Ilegal Sembilan Tahun di Lampung Selatan</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:55:54 +0700</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>TZ diketahui tinggal di Indonesia bersama istri yang merupakan Warga Negara Indonesia (WNI).</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7867248/menikah-dengan-wni-wn-myanmar-diduga-tinggal-ilegal-sembilan-tahun-di-lampung-selatan</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/nswN_7OrCveEcjrCs4k86F79ekQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Warga-Negara-asing-WNA-Myanmar.jpg</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Menko Polkam, Para Jenderal Bintang 4 TNI-Polri Hingga Jaksa Agung Kumpul di Markas Besar AL</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:55:33 +0700</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Menko Polkam mendorong penguatan komunikasi antarpimpinan dan antarlembaga untuk menjaga kekompakan dalam menjalankan tugas.</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7867247/menko-polkam-para-jenderal-bintang-4-tni-polri-hingga-jaksa-agung-kumpul-di-markas-besar-al</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/HzaxgOR1Vthc9JwaA7e9t2rpAC4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Djamari-Chaniago-kapolri-Jenderal_2.jpg</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Kebangkitan Singapura, The Lions Tak Lagi Jadi Penggembira di Piala AFF 2026</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:49:17 +0700</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Singapura bangkit bersama Gavin Lee dan menyingkirkan Indonesia. Kini, The Lions ditantang Thailand di semifinal Piala AFF 2026.</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7867246/kebangkitan-singapura-the-lions-tak-lagi-jadi-penggembira-di-piala-aff-2026</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/iboht6amQhsYVg3hY7SU_axQqZo=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Aksi-kiper-Timnas-Indonesia-Cahya-Supriadi-dan-Beckham-Putra-berusaha-meredam-pemain-Singapura.jpg</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Polisi Ungkap Kasus Penyekapan Lansia di Serpong, Pelaku Mengaku Anggota KPK</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:47:30 +0700</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Polsek Serpong bongkar kasus penyekapan lansia bermodus penipuan KPK, dua pelaku ditangkap cepat di Cianjur.</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7867245/polisi-ungkap-kasus-penyekapan-lansia-di-serpong-pelaku-mengaku-anggota-kpk</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/JIpr2jQOv7ODh62Fe5x5Bhe8EEo=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Kapolres-Tangerang-Selatan-AKBP-Boy-Jumalolo-tengah-didampingi-jajaran.jpg</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Mentan Amran: TNI yang Bantu Olah Lahan Warga Tak Dapat Tambahan Honor</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:46:36 +0700</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Prajurit TNI yang membantu mengelola lahan pertanian warga tidak mendapat tambahan honor.</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7867244/mentan-amran-tni-yang-bantu-olah-lahan-warga-tak-dapat-tambahan-honor</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Ce69G_uDo4PrARlGvMyvRSX8OIY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/amran-sulaiman-bulog-97.jpg</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Molly Prabawaty: Sidang Tahunan MPR RI Momentum Penting Perkuat Akuntabilitas Publik</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:44:09 +0700</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Molly Prabawaty sebut Sidang Tahunan MPR RI sebagai momentum penting untuk memperkuat akuntabilitas publik dan kinerja lembaga negara.</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/kilas-kementerian/7867243/molly-prabawaty-sidang-tahunan-mpr-ri-momentum-penting-perkuat-akuntabilitas-publik</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/SglsiPuC5dkH3SbiiZIIsQ76KsU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Molly-Prabawati-saat-menghadiri-Sidang-Tahunan-MPR-RI.jpg</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Cara Beli ETF Emas, Lengkap dengan Tickernya</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 10:10:28 +0700</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Mentari Puspadini</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Investasi emas kini lebih mudah dengan ETF emas di Indonesia. Dapatkan keuntungan dari pergerakan harga emas tanpa menyimpan fisik. Pelajari lebih lanjut!</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260812091054-17-758491/cara-beli-etf-emas-lengkap-dengan-tickernya</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/07/05/emas-batangan-ap-photo-2_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Purbaya Pede PFII Bisa Tarik Investasi Asing Lebih dari Rp500 T</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:50:45 +0700</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>chd</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Menkeu Purbaya optimis Pusat Finansial Internasional Indonesia (PFII) bisa menarik investasi hingga Rp500 triliun, tanpa kerugian fiskal bagi negara.</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260812081258-17-758447/purbaya-pede-pfii-bisa-tarik-investasi-asing-lebih-dari-rp500-t</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/03/menteri-keuangan-purbaya-yudhi-sadewa-saat-konferensi-pers-hasil-rapat-berskla-kssk-iii-tahun-2016-di-jakarta-senin-382026-1785746633916_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Video: IHSG Dibuka Menguat Tapi Rupiah Anjlok ke Rp17.840 per Dolar AS</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:36:27 +0700</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia TV</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>IHSG Menguat Tapi Rupiah Anjlok ke Level Rp 17.840 per Dolar AS</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260812093401-19-758490/video-ihsg-dibuka-menguat-tapi-rupiah-anjlok-ke-rp17840-per-dolar-as</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/12/ihsg-menguat-tapi-rupiah-anjlok-ke-level-rp-17840-per-dolar-as-1786502140159_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Harga Naik Tinggi, Bursa Pantau Ketat Pergerakan 2 Saham Ini</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:35:59 +0700</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Bursa Efek Indonesia memantau ketat saham DWGL dan GIAA karena Unusual Market Activity. Investor diimbau untuk cermati perkembangan dan kinerja emiten.</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260812084359-17-758456/harga-naik-tinggi-bursa-pantau-ketat-pergerakan-2-saham-ini</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/08/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-gedung-bursa-efek-indonesia-bei-jakarta-senin-862026-cnbc-ind-1780893013607_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Danantara Bikin Cuan BUMN Makin Tebal, Timah Pimpin Kenaikan Laba 804%</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:20:03 +0700</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>BPI Danantara melaporkan kinerja positif BUMN Semester I 2026. PT Timah tumbuh 804,7%, diikuti Pupuk Indonesia dan Semen Indonesia. BUMN merugi berbalik untung.</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260812085115-17-758458/danantara-bikin-cuan-bumn-makin-tebal-timah-pimpin-kenaikan-laba-804</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/08/25/proses-pengolahan-timah-di-pt-timah-cnbc-indonesiafirda-dwi-muliawati-1756098181354_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>IHSG Sesi I Dibuka Menguat 0,16% ke Level 6.277</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:05:22 +0700</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>IHSG menguat 0,16% di awal perdagangan Rabu (12/8/2026) setelah kemarin terkoreksi. Investor menanti rilis inflasi AS dan pengumuman MSCI Index Review.</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260812084604-17-758461/ihsg-sesi-i-dibuka-menguat-016-ke-level-6277</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/30/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-bursa-efek-indonesia-bei-jakarta-selasa-3062026-1782797019138_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Rupiah Dibuka Melemah, Dolar AS Naik ke Rp17.840</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:03:05 +0700</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Elvan Widyatama</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Tekanan terhadap rupiah kembali dirasakan pada perdagangan pagi ini. Mata uang Garuda kembali melemah terhadap dolar Amerika Serikat (AS).</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260812082744-17-758451/rupiah-dibuka-melemah-dolar-as-naik-ke-rp17840</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/08/petugas-menjunjukkan-uang-pecahan-dolar-amerika-serikat-as-dan-rupiah-di-dolar-asia-money-changer-jakarta-rabu-872026-1783496342241_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>IHSG Masih Volatil, Deretan Saham Ini Menarik Buat Dilirik</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:45:06 +0700</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>IHSG turun 1,53% ke 6.267,88. Sektor Industrials melemah, sementara Healthcare menguat. Rekomendasi saham hari ini termasuk TMAS, MEDC, dan WIRG.</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260812082529-17-758449/ihsg-masih-volatil-deretan-saham-ini-menarik-buat-dilirik</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/12/market-1786497928-1786497929120_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>IHSG Ambruk, Asing Terciduk Kompak Lepas 10 Saham Ini</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:39:55 +0700</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>IHSG melemah 1,53% ke 6.267,88, dengan 542 saham turun. Investor asing jual bersih Rp687,80 miliar. Simak 10 saham yang paling banyak dilepas!</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260812083441-17-758454/ihsg-ambruk-asing-terciduk-kompak-lepas-10-saham-ini</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/30/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-bursa-efek-indonesia-bei-jakarta-selasa-3062026-1782797018756_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Bursa Asia Dibuka Galau, Investor Tunggu Data Krusial AS</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:33:04 +0700</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Bursa saham Asia-Pasifik bervariasi, dengan investor fokus pada data inflasi AS. Indeks Kospi menguat, sementara Nikkei dan SdanP/ASX melemah.</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260812083024-17-758452/bursa-asia-dibuka-galau-investor-tunggu-data-krusial-as</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/04/04/japan-financial-markets-1743746448303_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Gandeng InJourney Dorong Wisata, Garuda Tebar 170.845 Tiket Gratis</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:29:22 +0700</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Garuda dan InJourney luncurkan program "Discover More Indonesia" untuk menarik wisatawan internasional dengan tiket domestik gratis. Program ini terbatas!</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260812082439-17-758450/gandeng-injourney-dorong-wisata-garuda-tebar-170845-tiket-gratis</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2018/03/01/6b941cef-409c-495a-b8c9-651fc5869a06_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Asing Pilih Serok 10 Saham Ini Kala IHSG Ambruk</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:24:02 +0700</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>IHSG melemah ke level 6.200, turun 1,53% pada 11 Agustus 2026. Investor asing mencatatkan penjualan bersih Rp687,80 miliar. Simak saham yang dibeli asing!</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260812082229-17-758448/asing-pilih-serok-10-saham-ini-kala-ihsg-ambruk</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/08/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-gedung-bursa-efek-indonesia-bei-jakarta-senin-862026-cnbc-ind-1780893013384_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Airlangga, Purbaya dan OJK-LPS Tanggapi Calon Bos BI Destry Damayanti</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Dukungan mengalir untuk Destry Damayanti sebagai calon Gubernur BI. Para pejabat menilai pengalaman dan rekam jejaknya di sektor keuangan sangat baik.</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260812075707-17-758444/airlangga-purbaya-ojk-lps-tanggapi-calon-bos-bi-destry-damayanti</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/03/pjs-gubernur-bank-indonesia-destry-damayanti-saat-konferensi-pers-hasil-rapat-berskla-kssk-iii-tahun-2016-di-jakarta-senin-382-1785749975910_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Nilai Pasar Modal RI Hampir Rp10.000 T, Airlangga Ungkap PR Besarnya</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:55:35 +0700</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>haa</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Pemerintah fokus pada penguatan kualitas pasar modal RI, meningkatkan kepercayaan investor, dan memperbaiki iklim investasi di tengah ketidakpastian global.</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260812063939-17-758433/nilai-pasar-modal-ri-hampir-rp10000-t-airlangga-ungkap-pr-besarnya</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/11/menko-perekonomian-airlangga-hartarto-dalam-acara-umkm-finance-summit-2026-dengan-tema-penguatan-akses-pembiayaan-dan-ekosiste-1786418466990_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>iOS 26 di iPhone Paling Baru Sudah Bisa Jailbreak, Ini Fungsinya</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:15:03 +0700</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Dopamine 3.0, jailbreak pertama untuk iOS 26, dirilis oleh pengembang opa334.</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260812091258-37-758474/ios-26-di-iphone-paling-baru-sudah-bisa-jailbreak-ini-fungsinya</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/10/17/calon-pembeli-melihat-iphone-17-series-di-gerai-ibox-kota-kasablanka-jakarta-jumat-17102025-cnbc-indonesiafaisal-rahman-1760684676968_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>China Balas Amerika, Respons Anak Buah Trump Tidak Terduga</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:15:00 +0700</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>China membalas pembatasan teknologi AS. FCC melarang impor perangkat dari China, sedangkan Beijing merespons dengan kontrol ekspor.</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260812080332-37-758445/china-balas-amerika-respons-anak-buah-trump-tidak-terduga</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/10/23/foto-kolase-bendera-amerika-serikat-dan-china-ireutersdado-ruvicillustrationfile-photo_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Indonesia Akan Dilewati Gerhana Matahari Total, Ini Jadwalnya</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Gerhana Matahari Total akan terjadi pada 12 Agustus 2026, namun tidak terlihat di Indonesia. Indonesia baru bisa melihatnya pada 2042.</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260812061116-37-758429/indonesia-akan-dilewati-gerhana-matahari-total-ini-jadwalnya</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/04/09/us-total-solar-eclipse-stretches-across-north-america-from-mexic_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Dikira Ngobrol dengan AI, Ternyata Cuma Satu Orang Balas Chat Seadanya</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 07:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>ChatTJB, layanan chatbot unik di San Francisco, dikelola oleh manusia, Tucker Bryant.</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260812061618-37-758430/dikira-ngobrol-dengan-ai-ternyata-cuma-satu-orang-balas-chat-seadanya</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/08/31/ilustrasi-pesan-singkat_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Kebutuhan Industri Berubah, Mahasiswa Desain Produk Didorong Lebih Adaptif</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Satria K Yudha</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Perubahan teknologi, kebutuhan pasar, dan tuntutan industri kreatif membuat desain produk tidak lagi hanya berkaitan dengan aspek estetika. Desainer dituntut mampu memahami kebutuhan pengguna, mengembangkan solusi berbasis...</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjmtd0416/kebutuhan-industri-berubah-mahasiswa-desain-produk-didorong-lebih-adaptif</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/_260812075855-850.png</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Momentum Hari UMKM Nasional, BRI Peduli Lakukan Pendampingan Berkelanjutan di Desa Brilian</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:42:40 +0700</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Ferry kisihandi</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, SLEMAN -- Usaha Mikro, Kecil, dan Menengah (UMKM) memiliki peran penting mendorong pertumbuhan ekonomi masyarakat sekaligus mengoptimalkan potensi ekonomi lokal.
+Memperingati Hari UMKM Nasional, 12 Agustus, BRI Peduli selaku...</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjmvf4472/momentum-hari-umkm-nasional-bri-peduli-lakukan-pendampingan-berkelanjutan-di-desa-brilian</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/melalui-berbagai-program-dan-inisiatif-ini-bri-terus-berupaya_260812084150-939.jpeg</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>KPK Buka Suara Soal Winda Lorenza, Diduga Saksi Bea Cukai yang Tewas di Medan</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 10:09:20 +0700</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Nama Winda Lorenza pernah dipanggil KPK tapi tidak hadir.</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267715/kpk-buka-suara-soal-winda-lorenza-diduga-saksi-bea-cukai-yang-tewas-di-medan</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/d7WVO8ipAvJbZHiwYBjIhC93hsI=/0x325:4032x2597/673x379/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/5303081/original/010753100_1754044504-1000408667.jpg</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Buang Sampah ke Jalan, Perusahaan Ini Didenda Pemprov DKI</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:37:26 +0700</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Penindakan dilakukan setelah DLH menelusuri kendaraan yang terekam membuang sampah di lokasi tersebut.</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267697/buang-sampah-ke-jalan-perusahaan-ini-didenda-pemprov-dki</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/GwgMOUKu1IdQJ-gEIXXgseb6f3E=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/8782451/original/096347000_1782887081-Cakung_Barat.jpeg</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Dakwaan KPK Bongkar Kuota Haji Tambahan Diatur Satu Pintu</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:36:41 +0700</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>JPU KPK Ungkap Skema Pengisian Kuota Haji Tambahan, Satu Pintu Lewat Bos Maktour</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267695/dakwaan-kpk-bongkar-kuota-haji-tambahan-diatur-satu-pintu</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/mlGDBBQWahbiTc4i5tj6lBtSorY=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/5484512/original/016624000_1769437759-3.jpg</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>BMKG Prediksi Hujan hingga Angin Kencang di Sejumlah Kota Besar</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:27:14 +0700</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>BMKG mengingatkan potensi hujan hingga angin kencang di sejumlah wilayah Indonesia.</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267689/bmkg-prediksi-hujan-hingga-angin-kencang-di-sejumlah-kota-besar</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/ln46k7Q_eN2eI3rDsGV02_wFvXI=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/3344534/original/094985600_1610178010-20210109-Waspada-Cuaca-Jakarta-3.jpg</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Warga Paseban Sulap Sampah Plastik Jadi Cuan</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:20:18 +0700</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Pengolahan Sampah Berbasis Warga di Kelurahan Paseban dilakukan dengan mengubah limbah plastik menjadi kerajinan bernilai guna dan ekonomis.</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267187/warga-paseban-sulap-sampah-plastik-jadi-cuan</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/1MzRQxAgwaSOgaB0GWI7goknfM0=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9297664/original/086562900_1784102286-ChatGPT_Image_15_Jul_2026__14.51.08.jpg</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Makam Sutrimo Dibongkar Hari Ini, Ini yang Dicari Penyidik</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 09:00:51 +0700</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>ekshumasi makam Sutrimo di Banyumas untuk mengungkap penyebab kematiannya melalui tiga tahap pemeriksaan forensik.</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267666/makam-sutrimo-dibongkar-hari-ini-ini-yang-dicari-penyidik</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/-fx7HAZbdkTLuLva3_Hw8lwALys=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9308334/original/005435400_1785137531-64336.jpg</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Didakwa Perkaya Diri Rp 93,6 Miliar, Mantan Stafus Eks Menag: Ini Kezaliman</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:48:00 +0700</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Mantan stafsus Menag, Ishfah Abidal Aziz, didakwa memperkaya diri Rp 93,6 Miliar dalam kasus korupsi kuota haji 2023-2024.</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267665/didakwa-perkaya-diri-rp-936-miliar-mantan-stafus-eks-menag-ini-kezaliman</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/9geUKRHCrj-kX7PCkn3Blkatkho=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9321711/original/022236500_1786499205-IMG_20260811_174636_698.jpg</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Rudi Tanoe Diperiksa KPK, Kerugian Negara Kasus Bansos Beras Dihitung</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:37:51 +0700</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>KPK bersama BPKP mendalami mekanisme distribusi dan kewajaran biaya penyaluran bansos beras untuk menghitung kerugian negara.</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267660/rudi-tanoe-diperiksa-kpk-kerugian-negara-kasus-bansos-beras-dihitung</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/cYgvVSSkr1LAnPTCETtvLPa8NRw=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/4065432/original/001612500_1656325087-WhatsApp_Image_2022-06-27_at_5.08.03_PM.jpeg</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Sidang MK, Dosen Singgung Pembangunan Universitas Republik Indonesia</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:07:21 +0700</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Dosen Aris Armunanto mendesak pemerintah fokus tingkatkan kesejahteraan dosen, ketimbang membangun Universitas Republik Indonesia.</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8267646/sidang-mk-dosen-singgung-pembangunan-universitas-republik-indonesia</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/tlVlFo-RDsaNAruenpogB6Zt1Q0=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/2992830/original/020508800_1576041384-IMG_2172.jpg</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Perkenalan Saepul dan Kunaefi Berujung Pembunuhan dan Mutilasi dalam Sehari</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 10:23:30 +0700</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Polisi ungkap rangkaian pembunuhan dan mutilasi pria di Depok. Pelaku awalnya mencari korban dari aplikasi Hornet untuk menguasai barang berharga.</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>https://megapolitan.kompas.com/read/2026/08/12/10230101/perkenalan-saepul-dan-kunaefi-berujung-pembunuhan-dan-mutilasi-dalam</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/ZP7eFZYX2KZ9cw2rHGXyLmCbLgo=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/11/6a7af46ae2df2.jpg</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Tiang Portal di Menteng Diduga Pesanan Pejabat, Bagaimana Aturannya?</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 10:23:30 +0700</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Tiang portal tiba-tiba muncul di Jalan Indramayu, Menteng, dan diduga atas permintaan pejabat. Warga mempertanyakan izin dan aturan pemasangannya.</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>https://megapolitan.kompas.com/read/2026/08/12/10081471/tiang-portal-di-menteng-diduga-pesanan-pejabat-bagaimana-aturannya</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/frkSg1OD3Dhe4hz8Bf311CQMRM0=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/12/6a7bb7d8c050c.jpg</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Naik DAMRI Bisa ke Kawah Ijen Banyuwangi, mulai Rp 20.000</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 10:23:30 +0700</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>DAMRI layani rute ke Kawah Ijen dari stasiun, Jawa Timur. Tarifnya mulai Rp 20.000.</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>https://travel.kompas.com/read/2026/08/12/095000927/naik-damri-bisa-ke-kawah-ijen-banyuwangi-mulai-rp-20.000</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/Ar4xjMfRWSwK-Ka0mpFsyuMBTus=/0x0:750x500/1200x675/filters:watermark(data/photo/2026/01/30/697c81889b5f6.png,0,-0,1)/data/photo/2025/09/02/68b6dd4625175.jpg</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I133"/>
+  <autoFilter ref="A1:I259"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>